--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534B9F16-FECA-456B-AC0E-103CE09484FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE0C3EA-950A-4F36-82E9-3AB764CEEB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile_config" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="176">
   <si>
     <t>GP8280</t>
   </si>
@@ -837,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C567"/>
+  <dimension ref="A1:C566"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -5578,29 +5578,29 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>416182</v>
+        <v>416070</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C431">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>416070</v>
+        <v>416069</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C432">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433">
-        <v>416069</v>
+      <c r="A433" t="s">
+        <v>124</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>1</v>
@@ -5610,8 +5610,8 @@
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A434" t="s">
-        <v>124</v>
+      <c r="A434">
+        <v>406340</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>1</v>
@@ -5622,7 +5622,7 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>406340</v>
+        <v>416301</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>1</v>
@@ -5633,35 +5633,35 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>416301</v>
+        <v>416119</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C436">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>416119</v>
+        <v>406081</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C437">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>406081</v>
+        <v>416068</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C438">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -5669,26 +5669,26 @@
         <v>416068</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C439">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>416068</v>
+        <v>736315</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C440">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>736315</v>
+        <v>736334</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>1</v>
@@ -5698,8 +5698,8 @@
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A442">
-        <v>736334</v>
+      <c r="A442" t="s">
+        <v>125</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>1</v>
@@ -5709,8 +5709,8 @@
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A443" t="s">
-        <v>125</v>
+      <c r="A443">
+        <v>406307</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>1</v>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>406307</v>
+        <v>466400</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>1</v>
@@ -5732,13 +5732,13 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>466400</v>
+        <v>416139</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C445">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -5746,7 +5746,7 @@
         <v>416139</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C446">
         <v>80</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>416139</v>
+        <v>416148</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>1</v>
@@ -5764,30 +5764,30 @@
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A448">
-        <v>416148</v>
+      <c r="A448" t="s">
+        <v>126</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C448">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C449">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>1</v>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>1</v>
@@ -5809,40 +5809,40 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C452">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C453">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C454">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>1</v>
@@ -5852,30 +5852,30 @@
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
-        <v>133</v>
+      <c r="A456">
+        <v>406310</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C456">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>134</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C457">
         <v>80</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A457">
-        <v>406310</v>
-      </c>
-      <c r="B457" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C457">
-        <v>90</v>
-      </c>
-    </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A458" t="s">
-        <v>134</v>
+      <c r="A458">
+        <v>416180</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>1</v>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459">
-        <v>416180</v>
+        <v>606180</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>1</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460">
-        <v>606180</v>
+        <v>656310</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>1</v>
@@ -5908,7 +5908,7 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461">
-        <v>656310</v>
+        <v>416311</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>1</v>
@@ -5919,7 +5919,7 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462">
-        <v>416311</v>
+        <v>406157</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>1</v>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463">
-        <v>406157</v>
+        <v>416182</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>1</v>
@@ -5941,18 +5941,18 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
-        <v>416182</v>
+        <v>406315</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C464">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
-        <v>406315</v>
+        <v>406312</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>1</v>
@@ -5962,19 +5962,19 @@
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466">
-        <v>406312</v>
+      <c r="A466" t="s">
+        <v>135</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C466">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>30</v>
@@ -5988,15 +5988,15 @@
         <v>136</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C468">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>1</v>
@@ -6006,14 +6006,14 @@
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A470" t="s">
-        <v>135</v>
+      <c r="A470">
+        <v>762013</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C470">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -6021,21 +6021,21 @@
         <v>762013</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C471">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A472">
-        <v>762013</v>
+      <c r="A472" t="s">
+        <v>137</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C472">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
@@ -6043,21 +6043,21 @@
         <v>137</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C473">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C474">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -6065,21 +6065,21 @@
         <v>138</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C475">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C476">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -6087,21 +6087,21 @@
         <v>139</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C477">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A478" t="s">
-        <v>139</v>
+      <c r="A478">
+        <v>242020</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C478">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -6109,21 +6109,21 @@
         <v>242020</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C479">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480">
-        <v>242020</v>
+        <v>602010</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C480">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -6131,21 +6131,21 @@
         <v>602010</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C481">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482">
-        <v>602010</v>
+        <v>652010</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C482">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -6153,37 +6153,37 @@
         <v>652010</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C483">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A484">
-        <v>652010</v>
+      <c r="A484" t="s">
+        <v>140</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C484">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C485">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>1</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>1</v>
@@ -6205,29 +6205,29 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C488">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C489">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>56</v>
@@ -6238,7 +6238,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>56</v>
@@ -6252,26 +6252,26 @@
         <v>143</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C492">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C493">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>30</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>30</v>
@@ -6293,29 +6293,29 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C496">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C497">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>1</v>
@@ -6326,29 +6326,29 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C499">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C500">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>56</v>
@@ -6362,26 +6362,26 @@
         <v>146</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C502">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C503">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>30</v>
@@ -6392,13 +6392,13 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C505">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -6406,10 +6406,10 @@
         <v>147</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C506">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -6417,18 +6417,18 @@
         <v>147</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C507">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A508" t="s">
-        <v>147</v>
+      <c r="A508">
+        <v>720004</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C508">
         <v>70</v>
@@ -6436,21 +6436,21 @@
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509">
-        <v>720004</v>
+        <v>720003</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C509">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C510">
         <v>0</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511">
-        <v>720004</v>
+        <v>720003</v>
       </c>
       <c r="B511" s="1" t="s">
         <v>56</v>
@@ -6472,32 +6472,32 @@
         <v>720003</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C512">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B513" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C513">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>720004</v>
+        <v>721001</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C514">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -6505,10 +6505,10 @@
         <v>721001</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C515">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -6516,7 +6516,7 @@
         <v>721001</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C516">
         <v>0</v>
@@ -6524,13 +6524,13 @@
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>721001</v>
+        <v>651030</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C517">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -6538,21 +6538,21 @@
         <v>651030</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C518">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519">
-        <v>651030</v>
+        <v>651010</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C519">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -6560,37 +6560,37 @@
         <v>651010</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C520">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A521">
-        <v>651010</v>
+      <c r="A521" t="s">
+        <v>148</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C521">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C522">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>1</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>1</v>
@@ -6612,10 +6612,10 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C525">
         <v>0</v>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>56</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>56</v>
@@ -6645,7 +6645,7 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>56</v>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -6667,7 +6667,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>30</v>
@@ -6678,7 +6678,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>30</v>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>30</v>
@@ -6700,32 +6700,32 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C533">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C534">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C535">
         <v>0</v>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>56</v>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>30</v>
@@ -6766,24 +6766,24 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C539">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C540">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -6791,32 +6791,32 @@
         <v>155</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C541">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C542">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C543">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -6824,18 +6824,18 @@
         <v>156</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C544">
-        <v>150</v>
+        <v>110</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A545" t="s">
-        <v>156</v>
+      <c r="A545">
+        <v>721014</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C545">
         <v>110</v>
@@ -6843,24 +6843,24 @@
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546">
-        <v>721014</v>
+        <v>721008</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C546">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547">
-        <v>721008</v>
+        <v>721005</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C547">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -6868,15 +6868,15 @@
         <v>721005</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C548">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549">
-        <v>721005</v>
+        <v>721008</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>1</v>
@@ -6887,24 +6887,24 @@
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550">
-        <v>721008</v>
+        <v>721014</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C550">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A551">
-        <v>721014</v>
+      <c r="A551" t="s">
+        <v>157</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C551">
-        <v>50</v>
+        <v>110</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -6912,32 +6912,32 @@
         <v>157</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C552">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A553" t="s">
-        <v>157</v>
+      <c r="A553">
+        <v>241040</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C553">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554">
-        <v>241040</v>
+        <v>241020</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C554">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6945,43 +6945,43 @@
         <v>241020</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C555">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556">
-        <v>241020</v>
+        <v>241040</v>
       </c>
       <c r="B556" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C556">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557">
-        <v>241040</v>
+        <v>601138</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C557">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558">
-        <v>601138</v>
+        <v>601128</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C558">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6989,54 +6989,54 @@
         <v>601128</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C559">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560">
-        <v>601128</v>
+        <v>601138</v>
       </c>
       <c r="B560" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C560">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A561">
-        <v>601138</v>
+      <c r="A561" t="s">
+        <v>158</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C561">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C562">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C563">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7044,42 +7044,31 @@
         <v>160</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C564">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C565">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C566">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A567" t="s">
-        <v>158</v>
-      </c>
-      <c r="B567" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C567">
         <v>50</v>
       </c>
     </row>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE0C3EA-950A-4F36-82E9-3AB764CEEB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8801E72E-BD58-444C-80F9-D0FF16E832B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,9 +426,6 @@
     <t>ZF0510</t>
   </si>
   <si>
-    <t>V00219740</t>
-  </si>
-  <si>
     <t>HS9050</t>
   </si>
   <si>
@@ -553,6 +550,9 @@
   </si>
   <si>
     <t>826801</t>
+  </si>
+  <si>
+    <t>VA9740</t>
   </si>
 </sst>
 </file>
@@ -840,7 +840,7 @@
   <dimension ref="A1:C566"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
     <col min="16384" max="16384" width="11.5703125" customWidth="1"/>
@@ -848,13 +848,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" t="s">
         <v>162</v>
       </c>
-      <c r="B1" t="s">
-        <v>163</v>
-      </c>
       <c r="C1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2289,7 +2289,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>30</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>30</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>30</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>30</v>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>30</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>30</v>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>30</v>
@@ -2377,7 +2377,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>30</v>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>30</v>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>30</v>
@@ -2410,7 +2410,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>30</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>30</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>1</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>1</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>1</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>1</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>1</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>1</v>
@@ -2498,7 +2498,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>1</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>1</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>1</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>1</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>1</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>1</v>
@@ -5864,7 +5864,7 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>1</v>
@@ -5963,7 +5963,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>30</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>30</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>1</v>
@@ -5996,7 +5996,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>1</v>
@@ -6029,7 +6029,7 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>30</v>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>1</v>
@@ -6051,7 +6051,7 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>30</v>
@@ -6062,7 +6062,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>1</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>30</v>
@@ -6084,7 +6084,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>1</v>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>1</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>1</v>
@@ -6183,7 +6183,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>1</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>1</v>
@@ -6205,7 +6205,7 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>56</v>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>56</v>
@@ -6227,7 +6227,7 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>56</v>
@@ -6238,7 +6238,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>56</v>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>30</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>30</v>
@@ -6271,7 +6271,7 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>30</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>30</v>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>1</v>
@@ -6304,7 +6304,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>1</v>
@@ -6315,7 +6315,7 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>1</v>
@@ -6326,7 +6326,7 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>56</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>56</v>
@@ -6348,7 +6348,7 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>56</v>
@@ -6359,7 +6359,7 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>30</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>30</v>
@@ -6381,7 +6381,7 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>30</v>
@@ -6392,7 +6392,7 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>1</v>
@@ -6403,7 +6403,7 @@
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>56</v>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>30</v>
@@ -6428,7 +6428,7 @@
         <v>720004</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C508">
         <v>70</v>
@@ -6439,7 +6439,7 @@
         <v>720003</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C509">
         <v>0</v>
@@ -6450,7 +6450,7 @@
         <v>720004</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C510">
         <v>0</v>
@@ -6461,7 +6461,7 @@
         <v>720003</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C511">
         <v>0</v>
@@ -6472,10 +6472,10 @@
         <v>720003</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C512">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -6483,7 +6483,7 @@
         <v>720004</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C513">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>721001</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C514">
         <v>70</v>
@@ -6505,7 +6505,7 @@
         <v>721001</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C515">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>721001</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C516">
         <v>0</v>
@@ -6568,7 +6568,7 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B521" s="1" t="s">
         <v>1</v>
@@ -6579,7 +6579,7 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>1</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>1</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>1</v>
@@ -6612,7 +6612,7 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B525" s="1" t="s">
         <v>56</v>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>56</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>56</v>
@@ -6645,7 +6645,7 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>56</v>
@@ -6656,7 +6656,7 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>30</v>
@@ -6667,7 +6667,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>30</v>
@@ -6678,7 +6678,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>30</v>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>30</v>
@@ -6700,7 +6700,7 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>1</v>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>1</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>56</v>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>56</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>30</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>30</v>
@@ -6766,7 +6766,7 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>30</v>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>30</v>
@@ -6788,7 +6788,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>1</v>
@@ -6799,7 +6799,7 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>1</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>30</v>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>1</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>30</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>1</v>
@@ -7008,7 +7008,7 @@
     </row>
     <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>30</v>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>30</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>30</v>
@@ -7041,7 +7041,7 @@
     </row>
     <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>1</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>1</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>1</v>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8801E72E-BD58-444C-80F9-D0FF16E832B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1383372-D573-4D5D-A10E-784E53A926AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile_config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -210,18 +221,6 @@
     <t>HS9080</t>
   </si>
   <si>
-    <t>GO 201</t>
-  </si>
-  <si>
-    <t>GO 202</t>
-  </si>
-  <si>
-    <t>GO 203</t>
-  </si>
-  <si>
-    <t>GO 209</t>
-  </si>
-  <si>
     <t>HO9820</t>
   </si>
   <si>
@@ -553,6 +552,18 @@
   </si>
   <si>
     <t>VA9740</t>
+  </si>
+  <si>
+    <t>GO2010</t>
+  </si>
+  <si>
+    <t>GO2020</t>
+  </si>
+  <si>
+    <t>GO2030</t>
+  </si>
+  <si>
+    <t>GO2090</t>
   </si>
 </sst>
 </file>
@@ -848,13 +859,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2289,7 +2300,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>30</v>
@@ -2311,7 +2322,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>30</v>
@@ -2322,7 +2333,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>30</v>
@@ -2333,7 +2344,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>30</v>
@@ -2344,7 +2355,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>30</v>
@@ -2355,7 +2366,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>30</v>
@@ -2366,7 +2377,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>30</v>
@@ -2377,7 +2388,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>30</v>
@@ -2388,7 +2399,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>30</v>
@@ -2399,7 +2410,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>30</v>
@@ -2410,7 +2421,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>30</v>
@@ -2421,7 +2432,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>30</v>
@@ -2432,7 +2443,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>1</v>
@@ -2443,7 +2454,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>1</v>
@@ -2454,7 +2465,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>1</v>
@@ -2465,7 +2476,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>1</v>
@@ -2476,7 +2487,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>1</v>
@@ -2487,7 +2498,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>1</v>
@@ -2498,7 +2509,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>1</v>
@@ -2509,7 +2520,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>1</v>
@@ -2520,7 +2531,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>1</v>
@@ -2531,7 +2542,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>1</v>
@@ -2542,7 +2553,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>1</v>
@@ -3048,7 +3059,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>1</v>
@@ -3059,7 +3070,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>1</v>
@@ -3070,7 +3081,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>63</v>
+        <v>174</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>1</v>
@@ -3081,7 +3092,7 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>64</v>
+        <v>175</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>1</v>
@@ -3202,7 +3213,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>1</v>
@@ -3213,7 +3224,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>30</v>
@@ -3224,7 +3235,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>1</v>
@@ -3279,7 +3290,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>30</v>
@@ -3301,7 +3312,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>30</v>
@@ -3323,7 +3334,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>1</v>
@@ -3345,7 +3356,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>1</v>
@@ -3356,7 +3367,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>1</v>
@@ -3367,7 +3378,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>1</v>
@@ -3455,7 +3466,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>1</v>
@@ -3466,7 +3477,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>30</v>
@@ -3477,7 +3488,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>1</v>
@@ -3488,7 +3499,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>30</v>
@@ -3499,7 +3510,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>30</v>
@@ -3510,7 +3521,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>30</v>
@@ -3521,7 +3532,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>30</v>
@@ -3620,7 +3631,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>1</v>
@@ -3631,7 +3642,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>1</v>
@@ -3642,7 +3653,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>1</v>
@@ -3653,7 +3664,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>1</v>
@@ -3664,7 +3675,7 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>30</v>
@@ -3675,7 +3686,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>30</v>
@@ -3686,7 +3697,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>1</v>
@@ -3697,7 +3708,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>1</v>
@@ -3708,7 +3719,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>30</v>
@@ -3719,7 +3730,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>30</v>
@@ -3730,7 +3741,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>30</v>
@@ -3763,7 +3774,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>30</v>
@@ -3774,7 +3785,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>30</v>
@@ -3807,7 +3818,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>1</v>
@@ -3818,7 +3829,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>1</v>
@@ -3851,7 +3862,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>1</v>
@@ -3862,7 +3873,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>1</v>
@@ -3873,7 +3884,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>1</v>
@@ -3884,7 +3895,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>30</v>
@@ -3917,7 +3928,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>1</v>
@@ -3942,7 +3953,7 @@
         <v>650050</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C282">
         <v>120</v>
@@ -3953,7 +3964,7 @@
         <v>650040</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C283">
         <v>90</v>
@@ -4159,7 +4170,7 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>30</v>
@@ -4170,7 +4181,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>1</v>
@@ -4181,7 +4192,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>30</v>
@@ -4192,7 +4203,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>1</v>
@@ -4203,10 +4214,10 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C306">
         <v>120</v>
@@ -4214,10 +4225,10 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -4258,7 +4269,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>30</v>
@@ -4269,7 +4280,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>1</v>
@@ -4280,7 +4291,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>30</v>
@@ -4291,7 +4302,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>1</v>
@@ -4302,7 +4313,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>1</v>
@@ -4324,7 +4335,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>30</v>
@@ -4335,7 +4346,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>30</v>
@@ -4346,7 +4357,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>30</v>
@@ -4357,7 +4368,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>30</v>
@@ -4368,7 +4379,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>30</v>
@@ -4379,7 +4390,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>30</v>
@@ -4390,7 +4401,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>30</v>
@@ -4412,7 +4423,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>30</v>
@@ -4489,7 +4500,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>1</v>
@@ -4511,7 +4522,7 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>1</v>
@@ -4522,7 +4533,7 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>1</v>
@@ -4533,7 +4544,7 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>1</v>
@@ -4544,7 +4555,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>1</v>
@@ -4555,7 +4566,7 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>1</v>
@@ -4566,7 +4577,7 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>1</v>
@@ -4577,7 +4588,7 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>1</v>
@@ -4588,7 +4599,7 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>30</v>
@@ -4599,7 +4610,7 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>30</v>
@@ -4610,7 +4621,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>30</v>
@@ -4621,7 +4632,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>1</v>
@@ -4632,7 +4643,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>1</v>
@@ -4643,7 +4654,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>1</v>
@@ -4742,7 +4753,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>30</v>
@@ -4753,7 +4764,7 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>30</v>
@@ -4764,7 +4775,7 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>30</v>
@@ -4775,7 +4786,7 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>30</v>
@@ -4786,7 +4797,7 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>1</v>
@@ -4797,7 +4808,7 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>1</v>
@@ -4808,7 +4819,7 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>1</v>
@@ -4819,7 +4830,7 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>1</v>
@@ -4830,7 +4841,7 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>30</v>
@@ -4841,7 +4852,7 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>30</v>
@@ -4852,7 +4863,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>30</v>
@@ -4863,7 +4874,7 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>30</v>
@@ -4874,7 +4885,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>1</v>
@@ -4885,7 +4896,7 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>1</v>
@@ -4896,7 +4907,7 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>1</v>
@@ -4907,7 +4918,7 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>1</v>
@@ -4918,7 +4929,7 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>30</v>
@@ -4929,7 +4940,7 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>30</v>
@@ -4940,7 +4951,7 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>1</v>
@@ -4951,7 +4962,7 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>1</v>
@@ -5039,7 +5050,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>1</v>
@@ -5050,7 +5061,7 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>30</v>
@@ -5061,7 +5072,7 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>1</v>
@@ -5072,7 +5083,7 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>30</v>
@@ -5083,7 +5094,7 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>1</v>
@@ -5094,7 +5105,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>30</v>
@@ -5105,7 +5116,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>1</v>
@@ -5116,7 +5127,7 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>30</v>
@@ -5127,7 +5138,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>1</v>
@@ -5138,7 +5149,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>30</v>
@@ -5149,7 +5160,7 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>1</v>
@@ -5270,7 +5281,7 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>30</v>
@@ -5281,7 +5292,7 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>1</v>
@@ -5402,7 +5413,7 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>30</v>
@@ -5413,7 +5424,7 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>1</v>
@@ -5424,7 +5435,7 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>30</v>
@@ -5435,7 +5446,7 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>1</v>
@@ -5446,7 +5457,7 @@
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>30</v>
@@ -5457,7 +5468,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>1</v>
@@ -5534,7 +5545,7 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>1</v>
@@ -5567,7 +5578,7 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>1</v>
@@ -5600,7 +5611,7 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>1</v>
@@ -5699,7 +5710,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>1</v>
@@ -5765,7 +5776,7 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>1</v>
@@ -5776,7 +5787,7 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>1</v>
@@ -5787,7 +5798,7 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>1</v>
@@ -5798,7 +5809,7 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>1</v>
@@ -5809,7 +5820,7 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>1</v>
@@ -5820,7 +5831,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>1</v>
@@ -5831,7 +5842,7 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>1</v>
@@ -5842,7 +5853,7 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>1</v>
@@ -5864,7 +5875,7 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>1</v>
@@ -5963,7 +5974,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>30</v>
@@ -5974,7 +5985,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>30</v>
@@ -5985,7 +5996,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>1</v>
@@ -5996,7 +6007,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>1</v>
@@ -6029,7 +6040,7 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>30</v>
@@ -6040,7 +6051,7 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>1</v>
@@ -6051,7 +6062,7 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>30</v>
@@ -6062,7 +6073,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>1</v>
@@ -6073,7 +6084,7 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>30</v>
@@ -6084,7 +6095,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>1</v>
@@ -6161,7 +6172,7 @@
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>1</v>
@@ -6172,7 +6183,7 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>1</v>
@@ -6183,7 +6194,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>1</v>
@@ -6194,7 +6205,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>1</v>
@@ -6205,7 +6216,7 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>56</v>
@@ -6216,7 +6227,7 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>56</v>
@@ -6227,7 +6238,7 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>56</v>
@@ -6238,7 +6249,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>56</v>
@@ -6249,7 +6260,7 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>30</v>
@@ -6260,7 +6271,7 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>30</v>
@@ -6271,7 +6282,7 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>30</v>
@@ -6282,7 +6293,7 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>30</v>
@@ -6293,7 +6304,7 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>1</v>
@@ -6304,7 +6315,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>1</v>
@@ -6315,7 +6326,7 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>1</v>
@@ -6326,7 +6337,7 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>56</v>
@@ -6337,7 +6348,7 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>56</v>
@@ -6348,7 +6359,7 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>56</v>
@@ -6359,7 +6370,7 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>30</v>
@@ -6370,7 +6381,7 @@
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>30</v>
@@ -6381,7 +6392,7 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>30</v>
@@ -6392,7 +6403,7 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>1</v>
@@ -6403,7 +6414,7 @@
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>56</v>
@@ -6414,7 +6425,7 @@
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>30</v>
@@ -6568,7 +6579,7 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B521" s="1" t="s">
         <v>1</v>
@@ -6579,7 +6590,7 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>1</v>
@@ -6590,7 +6601,7 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>1</v>
@@ -6601,7 +6612,7 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>1</v>
@@ -6612,7 +6623,7 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B525" s="1" t="s">
         <v>56</v>
@@ -6623,7 +6634,7 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>56</v>
@@ -6634,7 +6645,7 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>56</v>
@@ -6645,7 +6656,7 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>56</v>
@@ -6656,7 +6667,7 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>30</v>
@@ -6667,7 +6678,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>30</v>
@@ -6678,7 +6689,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>30</v>
@@ -6689,7 +6700,7 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>30</v>
@@ -6700,7 +6711,7 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>1</v>
@@ -6711,7 +6722,7 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>1</v>
@@ -6722,7 +6733,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>56</v>
@@ -6733,7 +6744,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>56</v>
@@ -6744,7 +6755,7 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>30</v>
@@ -6755,7 +6766,7 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>30</v>
@@ -6766,7 +6777,7 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>30</v>
@@ -6777,7 +6788,7 @@
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>30</v>
@@ -6788,7 +6799,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>1</v>
@@ -6799,7 +6810,7 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>1</v>
@@ -6810,7 +6821,7 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>30</v>
@@ -6821,7 +6832,7 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>1</v>
@@ -6898,7 +6909,7 @@
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>30</v>
@@ -6909,7 +6920,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>1</v>
@@ -7008,7 +7019,7 @@
     </row>
     <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>30</v>
@@ -7019,7 +7030,7 @@
     </row>
     <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>30</v>
@@ -7030,7 +7041,7 @@
     </row>
     <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>30</v>
@@ -7041,7 +7052,7 @@
     </row>
     <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>1</v>
@@ -7052,7 +7063,7 @@
     </row>
     <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>1</v>
@@ -7063,7 +7074,7 @@
     </row>
     <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>1</v>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1383372-D573-4D5D-A10E-784E53A926AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE59DF8-0FB9-4EF2-B1EA-445367DE920A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile_config" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="176">
   <si>
     <t>GP8280</t>
   </si>
@@ -848,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C566"/>
+  <dimension ref="A1:C569"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -3345,18 +3345,18 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227">
+        <v>426100</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C227">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228">
         <v>416112</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C227">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>63</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>1</v>
@@ -3367,7 +3367,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>1</v>
@@ -3378,21 +3378,21 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>65</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C230">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
         <v>66</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C230">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231">
-        <v>406115</v>
-      </c>
       <c r="B231" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C231">
         <v>80</v>
@@ -3403,21 +3403,21 @@
         <v>406115</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C232">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>666001</v>
+        <v>406115</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C233">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -3425,10 +3425,10 @@
         <v>666001</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C234">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -3436,54 +3436,54 @@
         <v>666001</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C235">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>550801</v>
+        <v>666001</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C236">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
+        <v>550801</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C237">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238">
         <v>553424</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C237">
+      <c r="B238" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C238">
         <v>100</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>67</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C238">
-        <v>150</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C239">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -3491,18 +3491,18 @@
         <v>68</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C240">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C241">
         <v>90</v>
@@ -3510,40 +3510,40 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C242">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C243">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>71</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C244">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
         <v>72</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C244">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245">
-        <v>721015</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>30</v>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>721009</v>
+        <v>721015</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>30</v>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>341040</v>
+        <v>721009</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>30</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>341030</v>
+        <v>341040</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>30</v>
@@ -3590,15 +3590,15 @@
         <v>341030</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C249">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>341040</v>
+        <v>341030</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>1</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>721009</v>
+        <v>341040</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>1</v>
@@ -3620,7 +3620,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>721015</v>
+        <v>721009</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>1</v>
@@ -3630,8 +3630,8 @@
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>72</v>
+      <c r="A253">
+        <v>721015</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>1</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>1</v>
@@ -3653,46 +3653,46 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C255">
-        <v>110</v>
+        <v>55</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C256">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C257">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -3700,37 +3700,37 @@
         <v>74</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C259">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C260">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C261">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>30</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>30</v>
@@ -3751,58 +3751,58 @@
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264">
-        <v>720024</v>
+      <c r="A264" t="s">
+        <v>77</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C264">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265">
+        <v>720024</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C265">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266">
         <v>720022</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C265">
+      <c r="B266" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C266">
         <v>70</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>78</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C266">
-        <v>80</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>78</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C267">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
         <v>79</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C267">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268">
-        <v>661000</v>
-      </c>
       <c r="B268" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C268">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -3810,15 +3810,15 @@
         <v>661000</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C269">
         <v>70</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>78</v>
+      <c r="A270">
+        <v>661000</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>1</v>
@@ -3829,7 +3829,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>1</v>
@@ -3839,8 +3839,8 @@
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272">
-        <v>720022</v>
+      <c r="A272" t="s">
+        <v>79</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>1</v>
@@ -3851,7 +3851,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>720024</v>
+        <v>720022</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>1</v>
@@ -3861,8 +3861,8 @@
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>77</v>
+      <c r="A274">
+        <v>720024</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>1</v>
@@ -3873,46 +3873,46 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C275">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C276">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>75</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
         <v>80</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C277">
+      <c r="B278" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C278">
         <v>100</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278">
-        <v>416210</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C278">
-        <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -3920,54 +3920,54 @@
         <v>416210</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>416210</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C280">
         <v>100</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
         <v>80</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C280">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281">
-        <v>406210</v>
-      </c>
       <c r="B281" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C281">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>650050</v>
+        <v>406210</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C282">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>650040</v>
+        <v>650050</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C283">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -3975,10 +3975,10 @@
         <v>650040</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C284">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -3986,21 +3986,21 @@
         <v>650040</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C285">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>650050</v>
+        <v>650040</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C286">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -4008,21 +4008,21 @@
         <v>650050</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C287">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>650020</v>
+        <v>650050</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C288">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -4030,21 +4030,21 @@
         <v>650020</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C289">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>600138</v>
+        <v>650020</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C290">
-        <v>170</v>
+        <v>100</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -4052,26 +4052,26 @@
         <v>600138</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C291">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>600121</v>
+        <v>600138</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C292">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>600127</v>
+        <v>600121</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>30</v>
@@ -4085,29 +4085,29 @@
         <v>600127</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C294">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>600121</v>
+        <v>600227</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C295">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>600128</v>
+        <v>600227</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C296">
         <v>150</v>
@@ -4115,282 +4115,282 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>600128</v>
+        <v>600127</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C297">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>650030</v>
+        <v>600121</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C298">
-        <v>170</v>
+        <v>90</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>650030</v>
+        <v>600128</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C299">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>660000</v>
+        <v>600128</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C300">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
+        <v>650030</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C301">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>650030</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C302">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303">
         <v>660000</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C301">
+      <c r="B303" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C303">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>660000</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C304">
         <v>80</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>82</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C302">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>82</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C303">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>83</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C304">
-        <v>0</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C305">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C306">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>83</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>83</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>83</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C309">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
         <v>82</v>
       </c>
-      <c r="B307" s="1" t="s">
+      <c r="B310" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C307">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308">
+      <c r="C310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311">
         <v>406670</v>
       </c>
-      <c r="B308" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C308">
+      <c r="B311" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C311">
         <v>110</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312">
         <v>406670</v>
       </c>
-      <c r="B309" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C309">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310">
+      <c r="B312" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313">
         <v>406316</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C310">
+      <c r="B313" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C313">
         <v>120</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>84</v>
-      </c>
-      <c r="B311" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C311">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>84</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C312">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>85</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C313">
-        <v>60</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C314">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>85</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C316">
         <v>60</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316">
-        <v>550800</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C316">
-        <v>80</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C317">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C318">
         <v>60</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>89</v>
+      <c r="A319">
+        <v>550800</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C319">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C320">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C321">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>30</v>
@@ -4401,7 +4401,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>30</v>
@@ -4411,66 +4411,66 @@
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324">
-        <v>720023</v>
+      <c r="A324" t="s">
+        <v>91</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C324">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C325">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326">
-        <v>240040</v>
+      <c r="A326" t="s">
+        <v>93</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C326">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>240030</v>
+        <v>720023</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C327">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328">
-        <v>240020</v>
+      <c r="A328" t="s">
+        <v>94</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C328">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>240020</v>
+        <v>240040</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C329">
         <v>60</v>
@@ -4481,7 +4481,7 @@
         <v>240030</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C330">
         <v>50</v>
@@ -4489,84 +4489,84 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>240040</v>
+        <v>240020</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C331">
         <v>50</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>94</v>
+      <c r="A332">
+        <v>240020</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C332">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>720023</v>
+        <v>240030</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C333">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>93</v>
+      <c r="A334">
+        <v>240040</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C334">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C335">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>91</v>
+      <c r="A336">
+        <v>720023</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C336">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C337">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>1</v>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>1</v>
@@ -4588,57 +4588,57 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C340">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C341">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C342">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C343">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C344">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -4646,76 +4646,76 @@
         <v>96</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C345">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
+        <v>97</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C346">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>97</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C347">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>96</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C348">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
         <v>95</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C346">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A347">
-        <v>722010</v>
-      </c>
-      <c r="B347" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C347">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A348">
-        <v>722005</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C348">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A349">
-        <v>722006</v>
-      </c>
       <c r="B349" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C349">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>722000</v>
+        <v>722010</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C350">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>722000</v>
+        <v>722005</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C351">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -4723,7 +4723,7 @@
         <v>722006</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -4731,79 +4731,79 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>722005</v>
+        <v>722000</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354">
+        <v>722000</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C354">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>722006</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>722005</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357">
         <v>722010</v>
       </c>
-      <c r="B354" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C354">
+      <c r="B357" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C357">
         <v>50</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
-        <v>98</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C355">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A356" t="s">
-        <v>99</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C356">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A357" t="s">
-        <v>100</v>
-      </c>
-      <c r="B357" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C357">
-        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C358">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C359">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -4811,62 +4811,62 @@
         <v>100</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C360">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C361">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C362">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C363">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C364">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -4874,24 +4874,24 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C366">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C367">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -4899,7 +4899,7 @@
         <v>104</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -4907,10 +4907,10 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -4918,7 +4918,7 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>1</v>
@@ -4929,29 +4929,29 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C371">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C372">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>1</v>
@@ -4965,59 +4965,59 @@
         <v>106</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C374">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>107</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C375">
         <v>60</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A375">
-        <v>406010</v>
-      </c>
-      <c r="B375" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C375">
-        <v>120</v>
-      </c>
-    </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A376">
-        <v>406321</v>
+      <c r="A376" t="s">
+        <v>107</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C376">
-        <v>150</v>
+        <v>70</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A377">
-        <v>406660</v>
+      <c r="A377" t="s">
+        <v>106</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C377">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378">
-        <v>406329</v>
+        <v>406010</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C378">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379">
-        <v>406325</v>
+        <v>406321</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>1</v>
@@ -5028,10 +5028,10 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380">
-        <v>416240</v>
+        <v>406660</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C380">
         <v>120</v>
@@ -5039,54 +5039,54 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
+        <v>406329</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C381">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>406325</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C382">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383">
         <v>416240</v>
       </c>
-      <c r="B381" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C381">
+      <c r="B383" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C383">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>416240</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C384">
         <v>100</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A382" t="s">
-        <v>108</v>
-      </c>
-      <c r="B382" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C382">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A383" t="s">
-        <v>109</v>
-      </c>
-      <c r="B383" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C383">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A384" t="s">
-        <v>109</v>
-      </c>
-      <c r="B384" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C384">
-        <v>120</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C385">
         <v>100</v>
@@ -5094,10 +5094,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C386">
         <v>100</v>
@@ -5105,120 +5105,120 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C387">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C388">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C389">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C390">
-        <v>130</v>
+        <v>100</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C391">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
+        <v>112</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C392">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>112</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C393">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
         <v>113</v>
       </c>
-      <c r="B392" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C392">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A393">
-        <v>242320</v>
-      </c>
-      <c r="B393" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C393">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A394">
-        <v>242320</v>
-      </c>
       <c r="B394" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C394">
         <v>100</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A395">
-        <v>651050</v>
+      <c r="A395" t="s">
+        <v>113</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C395">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396">
-        <v>651050</v>
+        <v>242320</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C396">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397">
-        <v>730010</v>
+        <v>242320</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C397">
         <v>100</v>
@@ -5226,241 +5226,241 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398">
-        <v>730010</v>
+        <v>651050</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C398">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399">
-        <v>731020</v>
+        <v>651050</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C399">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400">
-        <v>731020</v>
+        <v>730010</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C400">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401">
-        <v>476273</v>
+        <v>730010</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C401">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402">
+        <v>731020</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C402">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>731020</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C403">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404">
         <v>476273</v>
       </c>
-      <c r="B402" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C402">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
-        <v>114</v>
-      </c>
-      <c r="B403" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C403">
+      <c r="B404" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C404">
         <v>60</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A404" t="s">
-        <v>114</v>
-      </c>
-      <c r="B404" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C404">
-        <v>0</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405">
-        <v>466009</v>
+        <v>476273</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>114</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C406">
         <v>60</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406">
-        <v>466009</v>
-      </c>
-      <c r="B406" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C406">
-        <v>0</v>
-      </c>
-    </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407">
-        <v>416273</v>
+      <c r="A407" t="s">
+        <v>114</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C407">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408">
-        <v>416273</v>
+        <v>466009</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C408">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409">
-        <v>466023</v>
+        <v>466009</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C409">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410">
-        <v>466023</v>
+        <v>416273</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C410">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411">
-        <v>426200</v>
+        <v>416273</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C411">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412">
-        <v>426200</v>
+        <v>466023</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C412">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413">
-        <v>406272</v>
+        <v>466023</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C413">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414">
+        <v>426200</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C414">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>426200</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416">
         <v>406272</v>
       </c>
-      <c r="B414" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C414">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A415" t="s">
-        <v>115</v>
-      </c>
-      <c r="B415" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C415">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A416" t="s">
-        <v>115</v>
-      </c>
       <c r="B416" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C416">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A417" t="s">
-        <v>116</v>
+      <c r="A417">
+        <v>406272</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C417">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C418">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C419">
         <v>80</v>
@@ -5468,172 +5468,172 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
+        <v>116</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C420">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>116</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C421">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
         <v>117</v>
       </c>
-      <c r="B420" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C420">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A421">
-        <v>416338</v>
-      </c>
-      <c r="B421" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C421">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A422">
-        <v>416331</v>
-      </c>
       <c r="B422" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C422">
-        <v>200</v>
+        <v>80</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A423">
-        <v>416065</v>
+      <c r="A423" t="s">
+        <v>117</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C423">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>416067</v>
+        <v>416338</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C424">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>416086</v>
+        <v>416331</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C425">
-        <v>90</v>
+        <v>200</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>416096</v>
+        <v>416065</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C426">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>416067</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C427">
         <v>120</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A427" t="s">
-        <v>118</v>
-      </c>
-      <c r="B427" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C427">
-        <v>90</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>666003</v>
+        <v>416086</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C428">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>666002</v>
+        <v>416096</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C429">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C430">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>416070</v>
+        <v>666003</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C431">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>416069</v>
+        <v>666002</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C432">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C433">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>406340</v>
+        <v>416070</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C434">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>416301</v>
+        <v>416069</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>1</v>
@@ -5643,19 +5643,19 @@
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A436">
-        <v>416119</v>
+      <c r="A436" t="s">
+        <v>120</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C436">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>406081</v>
+        <v>406340</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>1</v>
@@ -5666,62 +5666,62 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>416068</v>
+        <v>416301</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C438">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>416068</v>
+        <v>416119</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C439">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>736315</v>
+        <v>406081</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C440">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>736334</v>
+        <v>416068</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C441">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A442" t="s">
-        <v>121</v>
+      <c r="A442">
+        <v>416068</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C442">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>406307</v>
+        <v>736315</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>1</v>
@@ -5732,7 +5732,7 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>466400</v>
+        <v>736334</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>1</v>
@@ -5742,118 +5742,118 @@
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A445">
-        <v>416139</v>
+      <c r="A445" t="s">
+        <v>121</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C445">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>416139</v>
+        <v>406307</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C446">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447">
+        <v>466400</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C447">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>416139</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C448">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>416139</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C449">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450">
         <v>416148</v>
       </c>
-      <c r="B447" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C447">
+      <c r="B450" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C450">
         <v>80</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
-        <v>122</v>
-      </c>
-      <c r="B448" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C448">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A449" t="s">
-        <v>123</v>
-      </c>
-      <c r="B449" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C449">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A450" t="s">
-        <v>124</v>
-      </c>
-      <c r="B450" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C450">
-        <v>100</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C451">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C452">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C453">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C454">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>1</v>
@@ -5863,8 +5863,8 @@
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456">
-        <v>406310</v>
+      <c r="A456" t="s">
+        <v>127</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>1</v>
@@ -5875,7 +5875,7 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>1</v>
@@ -5885,8 +5885,8 @@
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A458">
-        <v>416180</v>
+      <c r="A458" t="s">
+        <v>171</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>1</v>
@@ -5897,18 +5897,18 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459">
-        <v>606180</v>
+        <v>406310</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C459">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460">
-        <v>656310</v>
+      <c r="A460" t="s">
+        <v>129</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>1</v>
@@ -5919,7 +5919,7 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461">
-        <v>416311</v>
+        <v>416180</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>1</v>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462">
-        <v>406157</v>
+        <v>606180</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>1</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463">
-        <v>416182</v>
+        <v>656310</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>1</v>
@@ -5952,57 +5952,57 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
-        <v>406315</v>
+        <v>416311</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C464">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
+        <v>406157</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C465">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>416182</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C466">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>406315</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C467">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468">
         <v>406312</v>
       </c>
-      <c r="B465" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C465">
+      <c r="B468" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C468">
         <v>100</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466" t="s">
-        <v>130</v>
-      </c>
-      <c r="B466" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C466">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
-        <v>131</v>
-      </c>
-      <c r="B467" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C467">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A468" t="s">
-        <v>131</v>
-      </c>
-      <c r="B468" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C468">
-        <v>70</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -6010,227 +6010,227 @@
         <v>130</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C469">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>131</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C470">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>131</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C471">
         <v>70</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A470">
-        <v>762013</v>
-      </c>
-      <c r="B470" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C470">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A471">
-        <v>762013</v>
-      </c>
-      <c r="B471" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C471">
-        <v>60</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C472">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A473" t="s">
-        <v>132</v>
+      <c r="A473">
+        <v>762013</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C473">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>762013</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C474">
         <v>60</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A474" t="s">
-        <v>133</v>
-      </c>
-      <c r="B474" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C474">
-        <v>90</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C475">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C476">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
+        <v>133</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C477">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>133</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C478">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
         <v>134</v>
       </c>
-      <c r="B477" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C477">
+      <c r="B479" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C479">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>134</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C480">
         <v>60</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A478">
-        <v>242020</v>
-      </c>
-      <c r="B478" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C478">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A479">
-        <v>242020</v>
-      </c>
-      <c r="B479" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C479">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A480">
-        <v>602010</v>
-      </c>
-      <c r="B480" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C480">
-        <v>80</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481">
-        <v>602010</v>
+        <v>242020</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C481">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482">
-        <v>652010</v>
+        <v>242020</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C482">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483">
+        <v>602010</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C483">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>602010</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C484">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485">
         <v>652010</v>
       </c>
-      <c r="B483" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C483">
+      <c r="B485" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C485">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>652010</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C486">
         <v>60</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A484" t="s">
-        <v>135</v>
-      </c>
-      <c r="B484" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C484">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A485" t="s">
-        <v>136</v>
-      </c>
-      <c r="B485" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C485">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A486" t="s">
-        <v>137</v>
-      </c>
-      <c r="B486" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C486">
-        <v>0</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C487">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C488">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C489">
         <v>0</v>
@@ -6238,10 +6238,10 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C490">
         <v>0</v>
@@ -6249,24 +6249,24 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C491">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C492">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -6274,7 +6274,7 @@
         <v>137</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C493">
         <v>0</v>
@@ -6282,10 +6282,10 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C494">
         <v>0</v>
@@ -6293,32 +6293,32 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C495">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C496">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C497">
         <v>0</v>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C498">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         <v>139</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C499">
         <v>70</v>
@@ -6351,7 +6351,7 @@
         <v>140</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C500">
         <v>0</v>
@@ -6362,7 +6362,7 @@
         <v>141</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C501">
         <v>0</v>
@@ -6370,10 +6370,10 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C502">
         <v>70</v>
@@ -6384,7 +6384,7 @@
         <v>140</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C503">
         <v>0</v>
@@ -6392,10 +6392,10 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C504">
         <v>0</v>
@@ -6403,10 +6403,10 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C505">
         <v>70</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C506">
         <v>0</v>
@@ -6425,29 +6425,29 @@
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
+        <v>139</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
         <v>142</v>
       </c>
-      <c r="B507" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C507">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A508">
-        <v>720004</v>
-      </c>
       <c r="B508" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C508">
         <v>70</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A509">
-        <v>720003</v>
+      <c r="A509" t="s">
+        <v>142</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>56</v>
@@ -6457,25 +6457,25 @@
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A510">
-        <v>720004</v>
+      <c r="A510" t="s">
+        <v>142</v>
       </c>
       <c r="B510" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C510">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C511">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -6483,7 +6483,7 @@
         <v>720003</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C512">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>720004</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C513">
         <v>0</v>
@@ -6502,21 +6502,21 @@
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>721001</v>
+        <v>720003</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C514">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515">
-        <v>721001</v>
+        <v>720003</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C515">
         <v>0</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516">
-        <v>721001</v>
+        <v>720004</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>1</v>
@@ -6535,7 +6535,7 @@
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>651030</v>
+        <v>721001</v>
       </c>
       <c r="B517" s="1" t="s">
         <v>56</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518">
-        <v>651030</v>
+        <v>721001</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>30</v>
@@ -6557,54 +6557,54 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519">
-        <v>651010</v>
+        <v>721001</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C519">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520">
+        <v>651030</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C520">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A521">
+        <v>651030</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A522">
         <v>651010</v>
       </c>
-      <c r="B520" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C520">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A521" t="s">
-        <v>143</v>
-      </c>
-      <c r="B521" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C521">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A522" t="s">
-        <v>144</v>
-      </c>
       <c r="B522" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C522">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A523" t="s">
-        <v>145</v>
+      <c r="A523">
+        <v>651010</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C523">
         <v>0</v>
@@ -6612,21 +6612,21 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C524">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C525">
         <v>0</v>
@@ -6634,10 +6634,10 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C526">
         <v>0</v>
@@ -6645,10 +6645,10 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C527">
         <v>0</v>
@@ -6656,7 +6656,7 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>56</v>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C530">
         <v>0</v>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C531">
         <v>0</v>
@@ -6700,7 +6700,7 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>30</v>
@@ -6711,21 +6711,21 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C533">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C534">
         <v>0</v>
@@ -6733,10 +6733,10 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C535">
         <v>0</v>
@@ -6744,21 +6744,21 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C536">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -6766,10 +6766,10 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C538">
         <v>0</v>
@@ -6777,35 +6777,35 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C539">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C540">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C541">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -6813,26 +6813,26 @@
         <v>149</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C542">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C543">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>1</v>
@@ -6842,33 +6842,33 @@
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A545">
-        <v>721014</v>
+      <c r="A545" t="s">
+        <v>149</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C545">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A546">
-        <v>721008</v>
+      <c r="A546" t="s">
+        <v>151</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C546">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A547">
-        <v>721005</v>
+      <c r="A547" t="s">
+        <v>151</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C547">
         <v>110</v>
@@ -6876,13 +6876,13 @@
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548">
-        <v>721005</v>
+        <v>721014</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C548">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -6890,7 +6890,7 @@
         <v>721008</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C549">
         <v>60</v>
@@ -6898,29 +6898,29 @@
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550">
-        <v>721014</v>
+        <v>721005</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C550">
-        <v>50</v>
+        <v>110</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A551" t="s">
-        <v>152</v>
+      <c r="A551">
+        <v>721005</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C551">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A552" t="s">
-        <v>152</v>
+      <c r="A552">
+        <v>721008</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>1</v>
@@ -6931,79 +6931,79 @@
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553">
-        <v>241040</v>
+        <v>721014</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C553">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A554">
-        <v>241020</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>152</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C554">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A555">
-        <v>241020</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>152</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C555">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>241040</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C556">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557">
-        <v>601138</v>
+        <v>241020</v>
       </c>
       <c r="B557" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C557">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558">
-        <v>601128</v>
+        <v>241020</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C558">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559">
-        <v>601128</v>
+        <v>241040</v>
       </c>
       <c r="B559" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C559">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7011,54 +7011,54 @@
         <v>601138</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C560">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A561">
+        <v>601128</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C561">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A562">
+        <v>601128</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C562">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A563">
+        <v>601138</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C563">
         <v>60</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A561" t="s">
-        <v>153</v>
-      </c>
-      <c r="B561" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C561">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A562" t="s">
-        <v>154</v>
-      </c>
-      <c r="B562" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C562">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A563" t="s">
-        <v>155</v>
-      </c>
-      <c r="B563" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C563">
-        <v>0</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C564">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7066,20 +7066,53 @@
         <v>154</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C565">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
+        <v>155</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>155</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C567">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>154</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
         <v>153</v>
       </c>
-      <c r="B566" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C566">
+      <c r="B569" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C569">
         <v>50</v>
       </c>
     </row>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE59DF8-0FB9-4EF2-B1EA-445367DE920A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296A6783-A4A2-4B05-A2EC-7A64EF62713B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile_config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="177">
   <si>
     <t>GP8280</t>
   </si>
@@ -564,6 +564,9 @@
   </si>
   <si>
     <t>GO2090</t>
+  </si>
+  <si>
+    <t>P29537</t>
   </si>
 </sst>
 </file>
@@ -848,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C569"/>
+  <dimension ref="A1:C570"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -3458,7 +3461,7 @@
         <v>550801</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C237">
         <v>90</v>
@@ -3469,7 +3472,7 @@
         <v>553424</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C238">
         <v>100</v>
@@ -3510,7 +3513,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>69</v>
+        <v>176</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>30</v>
@@ -3521,40 +3524,40 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C243">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C244">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>71</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C245">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
         <v>72</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C245">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246">
-        <v>721015</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>30</v>
@@ -3565,7 +3568,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>721009</v>
+        <v>721015</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>30</v>
@@ -3576,7 +3579,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>341040</v>
+        <v>721009</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>30</v>
@@ -3587,7 +3590,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>341030</v>
+        <v>341040</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>30</v>
@@ -3601,15 +3604,15 @@
         <v>341030</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C250">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>341040</v>
+        <v>341030</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>1</v>
@@ -3620,7 +3623,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>721009</v>
+        <v>341040</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>1</v>
@@ -3631,7 +3634,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>721015</v>
+        <v>721009</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>1</v>
@@ -3641,8 +3644,8 @@
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>72</v>
+      <c r="A254">
+        <v>721015</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>1</v>
@@ -3653,7 +3656,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>1</v>
@@ -3664,46 +3667,46 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C256">
-        <v>110</v>
+        <v>55</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C258">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -3711,37 +3714,37 @@
         <v>74</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C260">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C261">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C262">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>30</v>
@@ -3752,7 +3755,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>30</v>
@@ -3762,58 +3765,58 @@
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265">
-        <v>720024</v>
+      <c r="A265" t="s">
+        <v>77</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C265">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266">
+        <v>720024</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C266">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267">
         <v>720022</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C266">
+      <c r="B267" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C267">
         <v>70</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>78</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C267">
-        <v>80</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>78</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C268">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
         <v>79</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C268">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269">
-        <v>661000</v>
-      </c>
       <c r="B269" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C269">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -3821,15 +3824,15 @@
         <v>661000</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C270">
         <v>70</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>78</v>
+      <c r="A271">
+        <v>661000</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>1</v>
@@ -3840,7 +3843,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>1</v>
@@ -3850,8 +3853,8 @@
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273">
-        <v>720022</v>
+      <c r="A273" t="s">
+        <v>79</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>1</v>
@@ -3862,7 +3865,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>720024</v>
+        <v>720022</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>1</v>
@@ -3872,8 +3875,8 @@
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>77</v>
+      <c r="A275">
+        <v>720024</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>1</v>
@@ -3884,46 +3887,46 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C276">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C277">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>75</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
         <v>80</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C278">
+      <c r="B279" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C279">
         <v>100</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279">
-        <v>416210</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C279">
-        <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -3931,54 +3934,54 @@
         <v>416210</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>416210</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C281">
         <v>100</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
         <v>80</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C281">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282">
-        <v>406210</v>
-      </c>
       <c r="B282" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C282">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>650050</v>
+        <v>406210</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C283">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>650040</v>
+        <v>650050</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C284">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -3986,10 +3989,10 @@
         <v>650040</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C285">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -3997,21 +4000,21 @@
         <v>650040</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C286">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>650050</v>
+        <v>650040</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C287">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -4019,21 +4022,21 @@
         <v>650050</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C288">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>650020</v>
+        <v>650050</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C289">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -4041,21 +4044,21 @@
         <v>650020</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C290">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>600138</v>
+        <v>650020</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C291">
-        <v>170</v>
+        <v>100</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -4063,26 +4066,26 @@
         <v>600138</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C292">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>600121</v>
+        <v>600138</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C293">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>600127</v>
+        <v>600121</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>30</v>
@@ -4093,7 +4096,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>600227</v>
+        <v>600127</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>30</v>
@@ -4107,26 +4110,26 @@
         <v>600227</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C296">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>600127</v>
+        <v>600227</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C297">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>600121</v>
+        <v>600127</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>1</v>
@@ -4137,13 +4140,13 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>600128</v>
+        <v>600121</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C299">
-        <v>150</v>
+        <v>90</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -4151,21 +4154,21 @@
         <v>600128</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C300">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>650030</v>
+        <v>600128</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C301">
-        <v>170</v>
+        <v>70</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -4173,21 +4176,21 @@
         <v>650030</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C302">
-        <v>70</v>
+        <v>170</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>660000</v>
+        <v>650030</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C303">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -4195,21 +4198,21 @@
         <v>660000</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C304">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>660000</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C305">
         <v>80</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>82</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C305">
-        <v>110</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -4217,18 +4220,18 @@
         <v>82</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C306">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -4239,7 +4242,7 @@
         <v>83</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -4250,32 +4253,32 @@
         <v>83</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C309">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C310">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311">
-        <v>406670</v>
+      <c r="A311" t="s">
+        <v>82</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C311">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -4283,32 +4286,32 @@
         <v>406670</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C312">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313">
+        <v>406670</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314">
         <v>406316</v>
       </c>
-      <c r="B313" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C313">
+      <c r="B314" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C314">
         <v>120</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>84</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C314">
-        <v>80</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -4316,21 +4319,21 @@
         <v>84</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C315">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C316">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -4338,59 +4341,59 @@
         <v>85</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C317">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
+        <v>85</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
         <v>86</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C318">
+      <c r="B319" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C319">
         <v>60</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320">
         <v>550800</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C319">
+      <c r="B320" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C320">
         <v>80</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>87</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C320">
-        <v>90</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C321">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>30</v>
@@ -4401,18 +4404,18 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C323">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>30</v>
@@ -4423,73 +4426,73 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C325">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
+        <v>92</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C326">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
         <v>93</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C326">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327">
+      <c r="B327" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328">
         <v>720023</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C327">
+      <c r="B328" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C328">
         <v>80</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
         <v>94</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C328">
+      <c r="B329" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C329">
         <v>70</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329">
-        <v>240040</v>
-      </c>
-      <c r="B329" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C329">
-        <v>60</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>240030</v>
+        <v>240040</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C330">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>240020</v>
+        <v>240030</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>30</v>
@@ -4503,26 +4506,26 @@
         <v>240020</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C332">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>240030</v>
+        <v>240020</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C333">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>240040</v>
+        <v>240030</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>1</v>
@@ -4532,8 +4535,8 @@
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>94</v>
+      <c r="A335">
+        <v>240040</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>1</v>
@@ -4543,19 +4546,19 @@
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336">
+      <c r="A336" t="s">
+        <v>94</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C336">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337">
         <v>720023</v>
-      </c>
-      <c r="B336" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C336">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>93</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>1</v>
@@ -4566,40 +4569,40 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C338">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C339">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C340">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>1</v>
@@ -4610,18 +4613,18 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C342">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>1</v>
@@ -4632,35 +4635,35 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C344">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C345">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C346">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -4668,15 +4671,15 @@
         <v>97</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C347">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>1</v>
@@ -4687,40 +4690,40 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>96</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
         <v>95</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C349">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350">
-        <v>722010</v>
-      </c>
       <c r="B350" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C350">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>722005</v>
+        <v>722010</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C351">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>722006</v>
+        <v>722005</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>30</v>
@@ -4731,13 +4734,13 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>722000</v>
+        <v>722006</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C353">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -4745,7 +4748,7 @@
         <v>722000</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C354">
         <v>60</v>
@@ -4753,18 +4756,18 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>722006</v>
+        <v>722000</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C355">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>722005</v>
+        <v>722006</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>1</v>
@@ -4775,40 +4778,40 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
+        <v>722005</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358">
         <v>722010</v>
       </c>
-      <c r="B357" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C357">
+      <c r="B358" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C358">
         <v>50</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A358" t="s">
-        <v>98</v>
-      </c>
-      <c r="B358" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C358">
-        <v>80</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C359">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>30</v>
@@ -4819,13 +4822,13 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C361">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -4833,7 +4836,7 @@
         <v>101</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C362">
         <v>60</v>
@@ -4841,29 +4844,29 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C363">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C364">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>1</v>
@@ -4874,40 +4877,40 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C366">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C367">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C368">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>30</v>
@@ -4921,26 +4924,26 @@
         <v>105</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C370">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C371">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>1</v>
@@ -4951,35 +4954,35 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C373">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C374">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C375">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -4987,70 +4990,70 @@
         <v>107</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C376">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
+        <v>107</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C377">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
         <v>106</v>
       </c>
-      <c r="B377" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C377">
+      <c r="B378" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C378">
         <v>60</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A378">
-        <v>406010</v>
-      </c>
-      <c r="B378" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C378">
-        <v>120</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379">
-        <v>406321</v>
+        <v>406010</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C379">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380">
-        <v>406660</v>
+        <v>406321</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C380">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
-        <v>406329</v>
+        <v>406660</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C381">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382">
-        <v>406325</v>
+        <v>406329</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>1</v>
@@ -5061,13 +5064,13 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383">
-        <v>416240</v>
+        <v>406325</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C383">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -5075,15 +5078,15 @@
         <v>416240</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C384">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
-        <v>108</v>
+      <c r="A385">
+        <v>416240</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>1</v>
@@ -5094,10 +5097,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C386">
         <v>100</v>
@@ -5108,21 +5111,21 @@
         <v>109</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C387">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C388">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -5130,7 +5133,7 @@
         <v>110</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C389">
         <v>100</v>
@@ -5138,10 +5141,10 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C390">
         <v>100</v>
@@ -5152,18 +5155,18 @@
         <v>111</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C391">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C392">
         <v>90</v>
@@ -5174,21 +5177,21 @@
         <v>112</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C393">
-        <v>130</v>
+        <v>90</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C394">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -5196,21 +5199,21 @@
         <v>113</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C395">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>113</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C396">
         <v>130</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A396">
-        <v>242320</v>
-      </c>
-      <c r="B396" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C396">
-        <v>100</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -5218,7 +5221,7 @@
         <v>242320</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C397">
         <v>100</v>
@@ -5226,13 +5229,13 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398">
-        <v>651050</v>
+        <v>242320</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C398">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -5240,7 +5243,7 @@
         <v>651050</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C399">
         <v>110</v>
@@ -5248,13 +5251,13 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400">
-        <v>730010</v>
+        <v>651050</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C400">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -5262,7 +5265,7 @@
         <v>730010</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C401">
         <v>100</v>
@@ -5270,10 +5273,10 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402">
-        <v>731020</v>
+        <v>730010</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C402">
         <v>100</v>
@@ -5284,21 +5287,21 @@
         <v>731020</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C403">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404">
-        <v>476273</v>
+        <v>731020</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C404">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -5306,21 +5309,21 @@
         <v>476273</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C405">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" t="s">
-        <v>114</v>
+      <c r="A406">
+        <v>476273</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C406">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -5328,21 +5331,21 @@
         <v>114</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C407">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A408">
-        <v>466009</v>
+      <c r="A408" t="s">
+        <v>114</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C408">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -5350,21 +5353,21 @@
         <v>466009</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C409">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410">
-        <v>416273</v>
+        <v>466009</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C410">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -5372,21 +5375,21 @@
         <v>416273</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C411">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412">
-        <v>466023</v>
+        <v>416273</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C412">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -5394,21 +5397,21 @@
         <v>466023</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C413">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414">
-        <v>426200</v>
+        <v>466023</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C414">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -5416,21 +5419,21 @@
         <v>426200</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C415">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416">
-        <v>406272</v>
+        <v>426200</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C416">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -5438,21 +5441,21 @@
         <v>406272</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C417">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A418" t="s">
-        <v>115</v>
+      <c r="A418">
+        <v>406272</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C418">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -5460,18 +5463,18 @@
         <v>115</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C419">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C420">
         <v>80</v>
@@ -5482,7 +5485,7 @@
         <v>116</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C421">
         <v>80</v>
@@ -5490,10 +5493,10 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C422">
         <v>80</v>
@@ -5504,147 +5507,147 @@
         <v>117</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C423">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A424">
-        <v>416338</v>
+      <c r="A424" t="s">
+        <v>117</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C424">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>416331</v>
+        <v>416338</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C425">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>416065</v>
+        <v>416331</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C426">
-        <v>90</v>
+        <v>200</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>416067</v>
+        <v>416065</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C427">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>416086</v>
+        <v>416067</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C428">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429">
+        <v>416086</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C429">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430">
         <v>416096</v>
       </c>
-      <c r="B429" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C429">
+      <c r="B430" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C430">
         <v>120</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
         <v>118</v>
       </c>
-      <c r="B430" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C430">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A431">
-        <v>666003</v>
-      </c>
       <c r="B431" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C431">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432">
+        <v>666003</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C432">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433">
         <v>666002</v>
       </c>
-      <c r="B432" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C432">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433" t="s">
+      <c r="B433" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C433">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
         <v>119</v>
       </c>
-      <c r="B433" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C433">
+      <c r="B434" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C434">
         <v>85</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A434">
-        <v>416070</v>
-      </c>
-      <c r="B434" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C434">
-        <v>90</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435">
+        <v>416070</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C435">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436">
         <v>416069</v>
-      </c>
-      <c r="B435" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C435">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A436" t="s">
-        <v>120</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>1</v>
@@ -5654,8 +5657,8 @@
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A437">
-        <v>406340</v>
+      <c r="A437" t="s">
+        <v>120</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>1</v>
@@ -5666,7 +5669,7 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>416301</v>
+        <v>406340</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>1</v>
@@ -5677,35 +5680,35 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>416119</v>
+        <v>416301</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C439">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>406081</v>
+        <v>416119</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C440">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>416068</v>
+        <v>406081</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C441">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -5713,48 +5716,48 @@
         <v>416068</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C442">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>736315</v>
+        <v>416068</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C443">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
+        <v>736315</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C444">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445">
         <v>736334</v>
       </c>
-      <c r="B444" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C444">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A445" t="s">
+      <c r="B445" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C445">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
         <v>121</v>
-      </c>
-      <c r="B445" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C445">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A446">
-        <v>406307</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>1</v>
@@ -5765,7 +5768,7 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>466400</v>
+        <v>406307</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>1</v>
@@ -5776,13 +5779,13 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>416139</v>
+        <v>466400</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C448">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -5790,7 +5793,7 @@
         <v>416139</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C449">
         <v>80</v>
@@ -5798,7 +5801,7 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>416148</v>
+        <v>416139</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>1</v>
@@ -5808,30 +5811,30 @@
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A451" t="s">
-        <v>122</v>
+      <c r="A451">
+        <v>416148</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C451">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C452">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>1</v>
@@ -5842,7 +5845,7 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>1</v>
@@ -5853,40 +5856,40 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C455">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C456">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C457">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>1</v>
@@ -5896,30 +5899,30 @@
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A459">
+      <c r="A459" t="s">
+        <v>171</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C459">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460">
         <v>406310</v>
       </c>
-      <c r="B459" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C459">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460" t="s">
+      <c r="B460" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C460">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
         <v>129</v>
-      </c>
-      <c r="B460" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C460">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A461">
-        <v>416180</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>1</v>
@@ -5930,7 +5933,7 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462">
-        <v>606180</v>
+        <v>416180</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>1</v>
@@ -5941,7 +5944,7 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463">
-        <v>656310</v>
+        <v>606180</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>1</v>
@@ -5952,7 +5955,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
-        <v>416311</v>
+        <v>656310</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>1</v>
@@ -5963,7 +5966,7 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
-        <v>406157</v>
+        <v>416311</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>1</v>
@@ -5974,7 +5977,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466">
-        <v>416182</v>
+        <v>406157</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>1</v>
@@ -5985,18 +5988,18 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467">
-        <v>406315</v>
+        <v>416182</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C467">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468">
-        <v>406312</v>
+        <v>406315</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>1</v>
@@ -6006,19 +6009,19 @@
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A469" t="s">
-        <v>130</v>
+      <c r="A469">
+        <v>406312</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C469">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>30</v>
@@ -6032,15 +6035,15 @@
         <v>131</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C471">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>1</v>
@@ -6050,14 +6053,14 @@
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A473">
-        <v>762013</v>
+      <c r="A473" t="s">
+        <v>130</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C473">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -6065,21 +6068,21 @@
         <v>762013</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C474">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>762013</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C475">
         <v>60</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A475" t="s">
-        <v>132</v>
-      </c>
-      <c r="B475" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C475">
-        <v>90</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -6087,21 +6090,21 @@
         <v>132</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C476">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C477">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -6109,21 +6112,21 @@
         <v>133</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C478">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C479">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -6131,21 +6134,21 @@
         <v>134</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C480">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>134</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C481">
         <v>60</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A481">
-        <v>242020</v>
-      </c>
-      <c r="B481" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C481">
-        <v>70</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -6153,21 +6156,21 @@
         <v>242020</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C482">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483">
-        <v>602010</v>
+        <v>242020</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C483">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -6175,21 +6178,21 @@
         <v>602010</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C484">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485">
-        <v>652010</v>
+        <v>602010</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C485">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -6197,37 +6200,37 @@
         <v>652010</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C486">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>652010</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C487">
         <v>60</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A487" t="s">
-        <v>135</v>
-      </c>
-      <c r="B487" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C487">
-        <v>70</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C488">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>1</v>
@@ -6238,7 +6241,7 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>1</v>
@@ -6249,29 +6252,29 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C491">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C492">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>56</v>
@@ -6282,7 +6285,7 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>56</v>
@@ -6296,26 +6299,26 @@
         <v>138</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C495">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C496">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>30</v>
@@ -6326,7 +6329,7 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>30</v>
@@ -6337,29 +6340,29 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C499">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C500">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>1</v>
@@ -6370,29 +6373,29 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C502">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C503">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>56</v>
@@ -6406,26 +6409,26 @@
         <v>141</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C505">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C506">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>30</v>
@@ -6436,13 +6439,13 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C508">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -6450,10 +6453,10 @@
         <v>142</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C509">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -6461,18 +6464,18 @@
         <v>142</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C510">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A511">
-        <v>720004</v>
+      <c r="A511" t="s">
+        <v>142</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C511">
         <v>70</v>
@@ -6480,21 +6483,21 @@
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C512">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513">
-        <v>720004</v>
+        <v>720003</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C513">
         <v>0</v>
@@ -6502,7 +6505,7 @@
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B514" s="1" t="s">
         <v>30</v>
@@ -6516,7 +6519,7 @@
         <v>720003</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C515">
         <v>0</v>
@@ -6524,7 +6527,7 @@
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516">
-        <v>720004</v>
+        <v>720003</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>1</v>
@@ -6535,13 +6538,13 @@
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>721001</v>
+        <v>720004</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C517">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -6549,10 +6552,10 @@
         <v>721001</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C518">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -6560,7 +6563,7 @@
         <v>721001</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C519">
         <v>0</v>
@@ -6568,13 +6571,13 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520">
-        <v>651030</v>
+        <v>721001</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C520">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -6582,21 +6585,21 @@
         <v>651030</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C521">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522">
-        <v>651010</v>
+        <v>651030</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C522">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -6604,37 +6607,37 @@
         <v>651010</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C523">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A524" t="s">
-        <v>143</v>
+      <c r="A524">
+        <v>651010</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C524">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B525" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C525">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>1</v>
@@ -6645,7 +6648,7 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>1</v>
@@ -6656,10 +6659,10 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C528">
         <v>0</v>
@@ -6667,7 +6670,7 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>56</v>
@@ -6678,7 +6681,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>56</v>
@@ -6689,7 +6692,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>56</v>
@@ -6700,10 +6703,10 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C532">
         <v>0</v>
@@ -6711,7 +6714,7 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>30</v>
@@ -6722,7 +6725,7 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>30</v>
@@ -6733,7 +6736,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>30</v>
@@ -6744,32 +6747,32 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C536">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C537">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C538">
         <v>0</v>
@@ -6777,7 +6780,7 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>56</v>
@@ -6788,10 +6791,10 @@
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C540">
         <v>0</v>
@@ -6799,7 +6802,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>30</v>
@@ -6810,24 +6813,24 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C542">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C543">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -6835,32 +6838,32 @@
         <v>150</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C544">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B545" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C545">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C546">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -6868,18 +6871,18 @@
         <v>151</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C547">
-        <v>110</v>
+        <v>150</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A548">
-        <v>721014</v>
+      <c r="A548" t="s">
+        <v>151</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C548">
         <v>110</v>
@@ -6887,24 +6890,24 @@
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549">
-        <v>721008</v>
+        <v>721014</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C549">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550">
-        <v>721005</v>
+        <v>721008</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C550">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -6912,15 +6915,15 @@
         <v>721005</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C551">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552">
-        <v>721008</v>
+        <v>721005</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>1</v>
@@ -6931,24 +6934,24 @@
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553">
+        <v>721008</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C553">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A554">
         <v>721014</v>
       </c>
-      <c r="B553" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C553">
+      <c r="B554" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C554">
         <v>50</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A554" t="s">
-        <v>152</v>
-      </c>
-      <c r="B554" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C554">
-        <v>110</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -6956,32 +6959,32 @@
         <v>152</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C555">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>152</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C556">
         <v>60</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A556">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A557">
         <v>241040</v>
       </c>
-      <c r="B556" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C556">
+      <c r="B557" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C557">
         <v>120</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A557">
-        <v>241020</v>
-      </c>
-      <c r="B557" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C557">
-        <v>70</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6989,43 +6992,43 @@
         <v>241020</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C558">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559">
-        <v>241040</v>
+        <v>241020</v>
       </c>
       <c r="B559" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C559">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560">
-        <v>601138</v>
+        <v>241040</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C560">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561">
-        <v>601128</v>
+        <v>601138</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C561">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7033,54 +7036,54 @@
         <v>601128</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C562">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563">
+        <v>601128</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C563">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A564">
         <v>601138</v>
       </c>
-      <c r="B563" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C563">
+      <c r="B564" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C564">
         <v>60</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A564" t="s">
-        <v>153</v>
-      </c>
-      <c r="B564" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C564">
-        <v>120</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C565">
-        <v>70</v>
+        <v>120</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C566">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7088,31 +7091,42 @@
         <v>155</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C567">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B568" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C568">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
+        <v>154</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
         <v>153</v>
       </c>
-      <c r="B569" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C569">
+      <c r="B570" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C570">
         <v>50</v>
       </c>
     </row>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296A6783-A4A2-4B05-A2EC-7A64EF62713B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A229512-8457-4BFA-B776-DDC13025683E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="177">
   <si>
     <t>GP8280</t>
   </si>
@@ -851,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C570"/>
+  <dimension ref="A1:C571"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -1379,29 +1379,29 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>413211</v>
+        <v>413115</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C48">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>413209</v>
+        <v>413211</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>413207</v>
+        <v>413209</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>1</v>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>413205</v>
+        <v>413207</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>1</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>413201</v>
+        <v>413205</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>1</v>
@@ -1434,29 +1434,29 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>413001</v>
+        <v>413201</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C53">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>413003</v>
+        <v>413001</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>413005</v>
+        <v>413003</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>1</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>413007</v>
+        <v>413005</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>1</v>
@@ -1478,29 +1478,29 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>413309</v>
+        <v>413007</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>413307</v>
+        <v>413309</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C58">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>413305</v>
+        <v>413307</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>1</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>413303</v>
+        <v>413305</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>1</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>413301</v>
+        <v>413303</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>1</v>
@@ -1533,18 +1533,18 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>443310</v>
+        <v>413301</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>413807</v>
+        <v>443310</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>1</v>
@@ -1555,18 +1555,18 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>413809</v>
+        <v>413807</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>413813</v>
+        <v>413809</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>1</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>413817</v>
+        <v>413813</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>1</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>413821</v>
+        <v>413817</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>1</v>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>413825</v>
+        <v>413821</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>1</v>
@@ -1610,29 +1610,29 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>413728</v>
+        <v>413825</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>413725</v>
+        <v>413728</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>413717</v>
+        <v>413725</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>1</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>413109</v>
+        <v>413717</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>1</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>413107</v>
+        <v>413109</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>1</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>413105</v>
+        <v>413107</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>1</v>
@@ -1676,24 +1676,24 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
+        <v>413105</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
         <v>413103</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>29</v>
-      </c>
       <c r="B76" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1701,21 +1701,21 @@
         <v>29</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1723,21 +1723,21 @@
         <v>31</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1745,21 +1745,21 @@
         <v>32</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1767,21 +1767,21 @@
         <v>33</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -1789,21 +1789,21 @@
         <v>34</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -1811,21 +1811,21 @@
         <v>35</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -1833,21 +1833,21 @@
         <v>36</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -1855,21 +1855,21 @@
         <v>37</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>416177</v>
+      <c r="A92" t="s">
+        <v>37</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -1877,21 +1877,21 @@
         <v>416177</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>416160</v>
+        <v>416177</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -1899,21 +1899,21 @@
         <v>416160</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>416382</v>
+        <v>416160</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -1921,21 +1921,21 @@
         <v>416382</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>426152</v>
+        <v>416382</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -1943,21 +1943,21 @@
         <v>426152</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>426150</v>
+        <v>426152</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -1965,21 +1965,21 @@
         <v>426150</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>426151</v>
+        <v>426150</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -1987,21 +1987,21 @@
         <v>426151</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>242310</v>
+        <v>426151</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2009,21 +2009,21 @@
         <v>242310</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>416168</v>
+        <v>242310</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2031,21 +2031,21 @@
         <v>416168</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>416157</v>
+        <v>416168</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2053,65 +2053,65 @@
         <v>416157</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>466005</v>
+        <v>416157</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
+        <v>466005</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
         <v>416146</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C111">
+      <c r="B112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C112">
         <v>50</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>38</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C112">
-        <v>180</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C113">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C114">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -2119,21 +2119,21 @@
         <v>40</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C115">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2141,21 +2141,21 @@
         <v>41</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>406225</v>
+      <c r="A118" t="s">
+        <v>41</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C118">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2163,26 +2163,26 @@
         <v>406225</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>606305</v>
+        <v>406225</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>656300</v>
+        <v>606305</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>1</v>
@@ -2193,29 +2193,29 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
+        <v>656300</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
         <v>656305</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C122">
+      <c r="B123" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123">
         <v>60</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>42</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C123">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>726004</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>30</v>
@@ -2226,24 +2226,24 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>726003</v>
+        <v>726004</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>246030</v>
+        <v>726003</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C126">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -2251,15 +2251,15 @@
         <v>246030</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C127">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>726003</v>
+        <v>246030</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>1</v>
@@ -2270,178 +2270,178 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
+        <v>726003</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
         <v>726004</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="B130" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>42</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130">
+      <c r="B131" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C131">
         <v>60</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
         <v>761016</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C131">
+      <c r="B132" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C132">
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>159</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C132">
+      <c r="B133" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C133">
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
         <v>416269</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C133">
+      <c r="B134" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C134">
         <v>150</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>160</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C134">
-        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C136">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C138">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C140">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C142">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C143">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C144">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -2449,7 +2449,7 @@
         <v>170</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C145">
         <v>120</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>1</v>
@@ -2468,62 +2468,62 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>1</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>1</v>
@@ -2545,51 +2545,51 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C157">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>30</v>
@@ -2600,10 +2600,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C159">
         <v>60</v>
@@ -2614,26 +2614,26 @@
         <v>46</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C160">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C161">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>1</v>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>1</v>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C164">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -2669,21 +2669,21 @@
         <v>47</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166">
-        <v>416274</v>
+      <c r="A166" t="s">
+        <v>47</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C166">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -2691,51 +2691,51 @@
         <v>416274</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168">
+        <v>416274</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>48</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C168">
+      <c r="B169" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C169">
         <v>150</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169">
-        <v>406320</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C169">
-        <v>120</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>416330</v>
+        <v>406320</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>406319</v>
+        <v>416330</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C171">
         <v>90</v>
@@ -2746,32 +2746,32 @@
         <v>406319</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C172">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>406323</v>
+        <v>406319</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C173">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>416251</v>
+        <v>406323</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C174">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -2779,21 +2779,21 @@
         <v>416251</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C175">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>416251</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C176">
         <v>80</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>49</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C176">
-        <v>100</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -2801,109 +2801,109 @@
         <v>49</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C177">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C178">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>50</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C179">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>51</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C179">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180">
+      <c r="B180" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C180">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
         <v>416264</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C180">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="B181" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C181">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>52</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C181">
+      <c r="B182" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C182">
         <v>110</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182">
-        <v>406255</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C182">
-        <v>100</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183">
+        <v>406255</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C183">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184">
         <v>416026</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C183">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>53</v>
-      </c>
       <c r="B184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C184">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C185">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C186">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -2911,21 +2911,21 @@
         <v>55</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C187">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C188">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -2933,70 +2933,70 @@
         <v>57</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C189">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190">
-        <v>406215</v>
+      <c r="A190" t="s">
+        <v>57</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C190">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191">
+        <v>406215</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C191">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192">
         <v>406266</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C191">
+      <c r="B192" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C192">
         <v>180</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
         <v>58</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C192">
+      <c r="B193" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C193">
         <v>140</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193">
-        <v>406271</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C193">
-        <v>160</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194">
+        <v>406271</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C194">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
         <v>656330</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C194">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>59</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>1</v>
@@ -3006,30 +3006,30 @@
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196">
-        <v>406295</v>
+      <c r="A196" t="s">
+        <v>59</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C196">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>406286</v>
+        <v>406295</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C197">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>406281</v>
+        <v>406286</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>1</v>
@@ -3039,14 +3039,14 @@
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>60</v>
+      <c r="A199">
+        <v>406281</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C199">
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -3054,76 +3054,76 @@
         <v>60</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C200">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C201">
-        <v>160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C202">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C203">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>174</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C204">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
         <v>175</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C204">
+      <c r="B205" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C205">
         <v>150</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205">
-        <v>716317</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C205">
-        <v>140</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>706290</v>
+        <v>716317</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C206">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -3131,37 +3131,37 @@
         <v>706290</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C207">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>416357</v>
+        <v>706290</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C208">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>416337</v>
+        <v>416357</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C209">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>416327</v>
+        <v>416337</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>1</v>
@@ -3172,13 +3172,13 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>416272</v>
+        <v>416327</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C211">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -3186,21 +3186,21 @@
         <v>416272</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C212">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>666000</v>
+        <v>416272</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C213">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -3208,29 +3208,29 @@
         <v>666000</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C214">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>666000</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C215">
         <v>130</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>61</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C215">
-        <v>90</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C216">
         <v>90</v>
@@ -3241,21 +3241,21 @@
         <v>62</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C217">
         <v>90</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218">
-        <v>406005</v>
+      <c r="A218" t="s">
+        <v>62</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C218">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -3263,92 +3263,92 @@
         <v>406005</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C219">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>716020</v>
+        <v>406005</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C220">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221">
+        <v>716020</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C221">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222">
         <v>736323</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C221">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>63</v>
-      </c>
       <c r="B222" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C222">
         <v>120</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223">
+      <c r="A223" t="s">
+        <v>63</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C223">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224">
         <v>416112</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C223">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+      <c r="B224" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C224">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
         <v>64</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C224">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225">
+      <c r="B225" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C225">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226">
         <v>426100</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C225">
+      <c r="B226" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C226">
         <v>80</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
         <v>64</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C226">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227">
-        <v>426100</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>1</v>
@@ -3359,18 +3359,18 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228">
+        <v>426100</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C228">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229">
         <v>416112</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C228">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>63</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>1</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>1</v>
@@ -3392,21 +3392,21 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>65</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C231">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
         <v>66</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C231">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232">
-        <v>406115</v>
-      </c>
       <c r="B232" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C232">
         <v>80</v>
@@ -3417,21 +3417,21 @@
         <v>406115</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C233">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>666001</v>
+        <v>406115</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C234">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -3439,10 +3439,10 @@
         <v>666001</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C235">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -3450,54 +3450,54 @@
         <v>666001</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C236">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>550801</v>
+        <v>666001</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C237">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238">
+        <v>550801</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C238">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239">
         <v>553424</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C238">
+      <c r="B239" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C239">
         <v>100</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>67</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C239">
-        <v>150</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C240">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -3505,18 +3505,18 @@
         <v>68</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C241">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>176</v>
+        <v>68</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C242">
         <v>90</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>69</v>
+        <v>176</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>30</v>
@@ -3535,40 +3535,40 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C244">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C245">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>71</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C246">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
         <v>72</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C246">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247">
-        <v>721015</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>30</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>721009</v>
+        <v>721015</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>30</v>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>341040</v>
+        <v>721009</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>30</v>
@@ -3601,7 +3601,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>341030</v>
+        <v>341040</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>30</v>
@@ -3615,15 +3615,15 @@
         <v>341030</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C251">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>341040</v>
+        <v>341030</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>1</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>721009</v>
+        <v>341040</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>1</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>721015</v>
+        <v>721009</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>1</v>
@@ -3655,8 +3655,8 @@
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>72</v>
+      <c r="A255">
+        <v>721015</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>1</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>1</v>
@@ -3678,46 +3678,46 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C257">
-        <v>110</v>
+        <v>55</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C259">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -3725,37 +3725,37 @@
         <v>74</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C261">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C262">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C263">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>30</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>30</v>
@@ -3776,58 +3776,58 @@
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266">
-        <v>720024</v>
+      <c r="A266" t="s">
+        <v>77</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C266">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267">
+        <v>720024</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C267">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268">
         <v>720022</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C267">
+      <c r="B268" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C268">
         <v>70</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>78</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C268">
-        <v>80</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>78</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C269">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
         <v>79</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C269">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270">
-        <v>661000</v>
-      </c>
       <c r="B270" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C270">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -3835,15 +3835,15 @@
         <v>661000</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C271">
         <v>70</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>78</v>
+      <c r="A272">
+        <v>661000</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>1</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>1</v>
@@ -3864,8 +3864,8 @@
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274">
-        <v>720022</v>
+      <c r="A274" t="s">
+        <v>79</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>1</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>720024</v>
+        <v>720022</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>1</v>
@@ -3886,8 +3886,8 @@
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>77</v>
+      <c r="A276">
+        <v>720024</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>1</v>
@@ -3898,46 +3898,46 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C277">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C278">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>75</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
         <v>80</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C279">
+      <c r="B280" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C280">
         <v>100</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280">
-        <v>416210</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C280">
-        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -3945,54 +3945,54 @@
         <v>416210</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>416210</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C282">
         <v>100</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
         <v>80</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C282">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283">
-        <v>406210</v>
-      </c>
       <c r="B283" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C283">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>650050</v>
+        <v>406210</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C284">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>650040</v>
+        <v>650050</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C285">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -4000,10 +4000,10 @@
         <v>650040</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C286">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -4011,21 +4011,21 @@
         <v>650040</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C287">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>650050</v>
+        <v>650040</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C288">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -4033,21 +4033,21 @@
         <v>650050</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C289">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>650020</v>
+        <v>650050</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C290">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -4055,21 +4055,21 @@
         <v>650020</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C291">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>600138</v>
+        <v>650020</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C292">
-        <v>170</v>
+        <v>100</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -4077,26 +4077,26 @@
         <v>600138</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C293">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>600121</v>
+        <v>600138</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C294">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>600127</v>
+        <v>600121</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>30</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>600227</v>
+        <v>600127</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>30</v>
@@ -4121,26 +4121,26 @@
         <v>600227</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C297">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>600127</v>
+        <v>600227</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C298">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>600121</v>
+        <v>600127</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>1</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>600128</v>
+        <v>600121</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C300">
-        <v>150</v>
+        <v>90</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -4165,21 +4165,21 @@
         <v>600128</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C301">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>650030</v>
+        <v>600128</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C302">
-        <v>170</v>
+        <v>70</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -4187,21 +4187,21 @@
         <v>650030</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C303">
-        <v>70</v>
+        <v>170</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>660000</v>
+        <v>650030</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C304">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -4209,21 +4209,21 @@
         <v>660000</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C305">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>660000</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C306">
         <v>80</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>82</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C306">
-        <v>110</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -4231,18 +4231,18 @@
         <v>82</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C307">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -4253,7 +4253,7 @@
         <v>83</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -4264,32 +4264,32 @@
         <v>83</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C310">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C311">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312">
-        <v>406670</v>
+      <c r="A312" t="s">
+        <v>82</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C312">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -4297,32 +4297,32 @@
         <v>406670</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C313">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314">
+        <v>406670</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315">
         <v>406316</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C314">
+      <c r="B315" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C315">
         <v>120</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>84</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C315">
-        <v>80</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -4330,21 +4330,21 @@
         <v>84</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C316">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C317">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -4352,59 +4352,59 @@
         <v>85</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C318">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>85</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
         <v>86</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C319">
+      <c r="B320" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C320">
         <v>60</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321">
         <v>550800</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C320">
+      <c r="B321" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C321">
         <v>80</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>87</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C321">
-        <v>90</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C322">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>30</v>
@@ -4415,18 +4415,18 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C324">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>30</v>
@@ -4437,73 +4437,73 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C326">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
+        <v>92</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C327">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
         <v>93</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C327">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328">
+      <c r="B328" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329">
         <v>720023</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C328">
+      <c r="B329" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C329">
         <v>80</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
         <v>94</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C329">
+      <c r="B330" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C330">
         <v>70</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330">
-        <v>240040</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C330">
-        <v>60</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>240030</v>
+        <v>240040</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C331">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>240020</v>
+        <v>240030</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>30</v>
@@ -4517,26 +4517,26 @@
         <v>240020</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C333">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>240030</v>
+        <v>240020</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C334">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>240040</v>
+        <v>240030</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>1</v>
@@ -4546,8 +4546,8 @@
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>94</v>
+      <c r="A336">
+        <v>240040</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>1</v>
@@ -4557,19 +4557,19 @@
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337">
+      <c r="A337" t="s">
+        <v>94</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C337">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338">
         <v>720023</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C337">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>93</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>1</v>
@@ -4580,40 +4580,40 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C339">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C340">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C341">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>1</v>
@@ -4624,18 +4624,18 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C343">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>1</v>
@@ -4646,35 +4646,35 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C345">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C346">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C347">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -4682,15 +4682,15 @@
         <v>97</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C348">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>1</v>
@@ -4701,40 +4701,40 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>96</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C350">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
         <v>95</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C350">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351">
-        <v>722010</v>
-      </c>
       <c r="B351" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C351">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>722005</v>
+        <v>722010</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C352">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>722006</v>
+        <v>722005</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>30</v>
@@ -4745,13 +4745,13 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>722000</v>
+        <v>722006</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C354">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -4759,7 +4759,7 @@
         <v>722000</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C355">
         <v>60</v>
@@ -4767,18 +4767,18 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>722006</v>
+        <v>722000</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C356">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>722005</v>
+        <v>722006</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>1</v>
@@ -4789,40 +4789,40 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358">
+        <v>722005</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359">
         <v>722010</v>
       </c>
-      <c r="B358" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C358">
+      <c r="B359" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C359">
         <v>50</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A359" t="s">
-        <v>98</v>
-      </c>
-      <c r="B359" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C359">
-        <v>80</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C360">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>30</v>
@@ -4833,13 +4833,13 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C362">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -4847,7 +4847,7 @@
         <v>101</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C363">
         <v>60</v>
@@ -4855,29 +4855,29 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C364">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C365">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>1</v>
@@ -4888,40 +4888,40 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C367">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C368">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C369">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>30</v>
@@ -4935,26 +4935,26 @@
         <v>105</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C371">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C372">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>1</v>
@@ -4965,35 +4965,35 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C374">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C375">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C376">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -5001,70 +5001,70 @@
         <v>107</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C377">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
+        <v>107</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C378">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
         <v>106</v>
       </c>
-      <c r="B378" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C378">
+      <c r="B379" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C379">
         <v>60</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A379">
-        <v>406010</v>
-      </c>
-      <c r="B379" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C379">
-        <v>120</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380">
-        <v>406321</v>
+        <v>406010</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C380">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
-        <v>406660</v>
+        <v>406321</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C381">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382">
-        <v>406329</v>
+        <v>406660</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C382">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383">
-        <v>406325</v>
+        <v>406329</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>1</v>
@@ -5075,13 +5075,13 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384">
-        <v>416240</v>
+        <v>406325</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C384">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -5089,15 +5089,15 @@
         <v>416240</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C385">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
-        <v>108</v>
+      <c r="A386">
+        <v>416240</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>1</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C387">
         <v>100</v>
@@ -5122,21 +5122,21 @@
         <v>109</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C388">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C389">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -5144,7 +5144,7 @@
         <v>110</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C390">
         <v>100</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C391">
         <v>100</v>
@@ -5166,18 +5166,18 @@
         <v>111</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C392">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C393">
         <v>90</v>
@@ -5188,21 +5188,21 @@
         <v>112</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C394">
-        <v>130</v>
+        <v>90</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C395">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -5210,21 +5210,21 @@
         <v>113</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C396">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>113</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C397">
         <v>130</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A397">
-        <v>242320</v>
-      </c>
-      <c r="B397" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C397">
-        <v>100</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -5232,7 +5232,7 @@
         <v>242320</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C398">
         <v>100</v>
@@ -5240,13 +5240,13 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399">
-        <v>651050</v>
+        <v>242320</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C399">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>651050</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C400">
         <v>110</v>
@@ -5262,13 +5262,13 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401">
-        <v>730010</v>
+        <v>651050</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C401">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -5276,7 +5276,7 @@
         <v>730010</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C402">
         <v>100</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403">
-        <v>731020</v>
+        <v>730010</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C403">
         <v>100</v>
@@ -5298,21 +5298,21 @@
         <v>731020</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C404">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405">
-        <v>476273</v>
+        <v>731020</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C405">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -5320,21 +5320,21 @@
         <v>476273</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C406">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
-        <v>114</v>
+      <c r="A407">
+        <v>476273</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C407">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -5342,21 +5342,21 @@
         <v>114</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C408">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A409">
-        <v>466009</v>
+      <c r="A409" t="s">
+        <v>114</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C409">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -5364,21 +5364,21 @@
         <v>466009</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C410">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411">
-        <v>416273</v>
+        <v>466009</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C411">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -5386,21 +5386,21 @@
         <v>416273</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C412">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413">
-        <v>466023</v>
+        <v>416273</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C413">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -5408,21 +5408,21 @@
         <v>466023</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C414">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415">
-        <v>426200</v>
+        <v>466023</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C415">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -5430,21 +5430,21 @@
         <v>426200</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C416">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417">
-        <v>406272</v>
+        <v>426200</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C417">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -5452,21 +5452,21 @@
         <v>406272</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C418">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A419" t="s">
-        <v>115</v>
+      <c r="A419">
+        <v>406272</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C419">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -5474,18 +5474,18 @@
         <v>115</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C420">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C421">
         <v>80</v>
@@ -5496,7 +5496,7 @@
         <v>116</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C422">
         <v>80</v>
@@ -5504,10 +5504,10 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C423">
         <v>80</v>
@@ -5518,147 +5518,147 @@
         <v>117</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C424">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A425">
-        <v>416338</v>
+      <c r="A425" t="s">
+        <v>117</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C425">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>416331</v>
+        <v>416338</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C426">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>416065</v>
+        <v>416331</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C427">
-        <v>90</v>
+        <v>200</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>416067</v>
+        <v>416065</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C428">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>416086</v>
+        <v>416067</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C429">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430">
+        <v>416086</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C430">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431">
         <v>416096</v>
       </c>
-      <c r="B430" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C430">
+      <c r="B431" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C431">
         <v>120</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A431" t="s">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
         <v>118</v>
       </c>
-      <c r="B431" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C431">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A432">
-        <v>666003</v>
-      </c>
       <c r="B432" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C432">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433">
+        <v>666003</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C433">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434">
         <v>666002</v>
       </c>
-      <c r="B433" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C433">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A434" t="s">
+      <c r="B434" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C434">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
         <v>119</v>
       </c>
-      <c r="B434" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C434">
+      <c r="B435" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C435">
         <v>85</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A435">
-        <v>416070</v>
-      </c>
-      <c r="B435" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C435">
-        <v>90</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436">
+        <v>416070</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C436">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437">
         <v>416069</v>
-      </c>
-      <c r="B436" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C436">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A437" t="s">
-        <v>120</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>1</v>
@@ -5668,8 +5668,8 @@
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A438">
-        <v>406340</v>
+      <c r="A438" t="s">
+        <v>120</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>1</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>416301</v>
+        <v>406340</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>1</v>
@@ -5691,35 +5691,35 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>416119</v>
+        <v>416301</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C440">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>406081</v>
+        <v>416119</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C441">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>416068</v>
+        <v>406081</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C442">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -5727,48 +5727,48 @@
         <v>416068</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C443">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>736315</v>
+        <v>416068</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C444">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445">
+        <v>736315</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C445">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446">
         <v>736334</v>
       </c>
-      <c r="B445" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C445">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A446" t="s">
+      <c r="B446" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C446">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
         <v>121</v>
-      </c>
-      <c r="B446" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C446">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A447">
-        <v>406307</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>1</v>
@@ -5779,7 +5779,7 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>466400</v>
+        <v>406307</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>1</v>
@@ -5790,13 +5790,13 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>416139</v>
+        <v>466400</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C449">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -5804,7 +5804,7 @@
         <v>416139</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C450">
         <v>80</v>
@@ -5812,7 +5812,7 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451">
-        <v>416148</v>
+        <v>416139</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>1</v>
@@ -5822,30 +5822,30 @@
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A452" t="s">
-        <v>122</v>
+      <c r="A452">
+        <v>416148</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C452">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C453">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>1</v>
@@ -5856,7 +5856,7 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>1</v>
@@ -5867,40 +5867,40 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C456">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C457">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C458">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>1</v>
@@ -5910,30 +5910,30 @@
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460">
+      <c r="A460" t="s">
+        <v>171</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C460">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461">
         <v>406310</v>
       </c>
-      <c r="B460" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C460">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A461" t="s">
+      <c r="B461" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C461">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
         <v>129</v>
-      </c>
-      <c r="B461" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C461">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462">
-        <v>416180</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>1</v>
@@ -5944,7 +5944,7 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463">
-        <v>606180</v>
+        <v>416180</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>1</v>
@@ -5955,7 +5955,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
-        <v>656310</v>
+        <v>606180</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>1</v>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
-        <v>416311</v>
+        <v>656310</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>1</v>
@@ -5977,7 +5977,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466">
-        <v>406157</v>
+        <v>416311</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>1</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467">
-        <v>416182</v>
+        <v>406157</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>1</v>
@@ -5999,18 +5999,18 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468">
-        <v>406315</v>
+        <v>416182</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C468">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469">
-        <v>406312</v>
+        <v>406315</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>1</v>
@@ -6020,19 +6020,19 @@
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A470" t="s">
-        <v>130</v>
+      <c r="A470">
+        <v>406312</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C470">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>30</v>
@@ -6046,15 +6046,15 @@
         <v>131</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C472">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>1</v>
@@ -6064,14 +6064,14 @@
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A474">
-        <v>762013</v>
+      <c r="A474" t="s">
+        <v>130</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C474">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -6079,21 +6079,21 @@
         <v>762013</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C475">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>762013</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C476">
         <v>60</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A476" t="s">
-        <v>132</v>
-      </c>
-      <c r="B476" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C476">
-        <v>90</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -6101,21 +6101,21 @@
         <v>132</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C477">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C478">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -6123,21 +6123,21 @@
         <v>133</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C479">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C480">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -6145,21 +6145,21 @@
         <v>134</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C481">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>134</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C482">
         <v>60</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A482">
-        <v>242020</v>
-      </c>
-      <c r="B482" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C482">
-        <v>70</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -6167,21 +6167,21 @@
         <v>242020</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C483">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484">
-        <v>602010</v>
+        <v>242020</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C484">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -6189,21 +6189,21 @@
         <v>602010</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C485">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486">
-        <v>652010</v>
+        <v>602010</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C486">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -6211,37 +6211,37 @@
         <v>652010</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C487">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488">
+        <v>652010</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C488">
         <v>60</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A488" t="s">
-        <v>135</v>
-      </c>
-      <c r="B488" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C488">
-        <v>70</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C489">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>1</v>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>1</v>
@@ -6263,29 +6263,29 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C492">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C493">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>56</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>56</v>
@@ -6310,26 +6310,26 @@
         <v>138</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C496">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C497">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>30</v>
@@ -6340,7 +6340,7 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>30</v>
@@ -6351,29 +6351,29 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C500">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C501">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>1</v>
@@ -6384,29 +6384,29 @@
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C503">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C504">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>56</v>
@@ -6420,26 +6420,26 @@
         <v>141</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C506">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C507">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>30</v>
@@ -6450,13 +6450,13 @@
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C509">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -6464,10 +6464,10 @@
         <v>142</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C510">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -6475,18 +6475,18 @@
         <v>142</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C511">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A512">
-        <v>720004</v>
+      <c r="A512" t="s">
+        <v>142</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C512">
         <v>70</v>
@@ -6494,21 +6494,21 @@
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B513" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C513">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>720004</v>
+        <v>720003</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C514">
         <v>0</v>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B515" s="1" t="s">
         <v>30</v>
@@ -6530,7 +6530,7 @@
         <v>720003</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C516">
         <v>0</v>
@@ -6538,7 +6538,7 @@
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>720004</v>
+        <v>720003</v>
       </c>
       <c r="B517" s="1" t="s">
         <v>1</v>
@@ -6549,13 +6549,13 @@
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518">
-        <v>721001</v>
+        <v>720004</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C518">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -6563,10 +6563,10 @@
         <v>721001</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C519">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -6574,7 +6574,7 @@
         <v>721001</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C520">
         <v>0</v>
@@ -6582,13 +6582,13 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521">
-        <v>651030</v>
+        <v>721001</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C521">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -6596,21 +6596,21 @@
         <v>651030</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C522">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523">
-        <v>651010</v>
+        <v>651030</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C523">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -6618,37 +6618,37 @@
         <v>651010</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C524">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A525" t="s">
-        <v>143</v>
+      <c r="A525">
+        <v>651010</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C525">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C526">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>1</v>
@@ -6659,7 +6659,7 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>1</v>
@@ -6670,10 +6670,10 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>56</v>
@@ -6692,7 +6692,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>56</v>
@@ -6703,7 +6703,7 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>56</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C533">
         <v>0</v>
@@ -6725,7 +6725,7 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>30</v>
@@ -6736,7 +6736,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>30</v>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>30</v>
@@ -6758,32 +6758,32 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C537">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C538">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C539">
         <v>0</v>
@@ -6791,7 +6791,7 @@
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>56</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C541">
         <v>0</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>30</v>
@@ -6824,24 +6824,24 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C543">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C544">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -6849,32 +6849,32 @@
         <v>150</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C545">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C546">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C547">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -6882,18 +6882,18 @@
         <v>151</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C548">
-        <v>110</v>
+        <v>150</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A549">
-        <v>721014</v>
+      <c r="A549" t="s">
+        <v>151</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C549">
         <v>110</v>
@@ -6901,24 +6901,24 @@
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550">
-        <v>721008</v>
+        <v>721014</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C550">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551">
-        <v>721005</v>
+        <v>721008</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C551">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -6926,15 +6926,15 @@
         <v>721005</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C552">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553">
-        <v>721008</v>
+        <v>721005</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>1</v>
@@ -6945,24 +6945,24 @@
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554">
+        <v>721008</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C554">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A555">
         <v>721014</v>
       </c>
-      <c r="B554" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C554">
+      <c r="B555" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C555">
         <v>50</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A555" t="s">
-        <v>152</v>
-      </c>
-      <c r="B555" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C555">
-        <v>110</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -6970,32 +6970,32 @@
         <v>152</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C556">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>152</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C557">
         <v>60</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A557">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A558">
         <v>241040</v>
       </c>
-      <c r="B557" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C557">
+      <c r="B558" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C558">
         <v>120</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A558">
-        <v>241020</v>
-      </c>
-      <c r="B558" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C558">
-        <v>70</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7003,43 +7003,43 @@
         <v>241020</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C559">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560">
-        <v>241040</v>
+        <v>241020</v>
       </c>
       <c r="B560" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C560">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561">
-        <v>601138</v>
+        <v>241040</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C561">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562">
-        <v>601128</v>
+        <v>601138</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C562">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7047,54 +7047,54 @@
         <v>601128</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C563">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564">
+        <v>601128</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C564">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A565">
         <v>601138</v>
       </c>
-      <c r="B564" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C564">
+      <c r="B565" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C565">
         <v>60</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A565" t="s">
-        <v>153</v>
-      </c>
-      <c r="B565" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C565">
-        <v>120</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C566">
-        <v>70</v>
+        <v>120</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B567" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C567">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7102,31 +7102,42 @@
         <v>155</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C568">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B569" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C569">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
+        <v>154</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
         <v>153</v>
       </c>
-      <c r="B570" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C570">
+      <c r="B571" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C571">
         <v>50</v>
       </c>
     </row>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A229512-8457-4BFA-B776-DDC13025683E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E54640-831E-41BC-A3ED-7FFD86ECDBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="177">
   <si>
     <t>GP8280</t>
   </si>
@@ -851,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C571"/>
+  <dimension ref="A1:C572"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -2028,13 +2028,13 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>416168</v>
+        <v>416269</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2042,21 +2042,21 @@
         <v>416168</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>416157</v>
+        <v>416168</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2064,65 +2064,65 @@
         <v>416157</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>466005</v>
+        <v>416157</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
+        <v>466005</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
         <v>416146</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C112">
+      <c r="B113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C113">
         <v>50</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>38</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C113">
-        <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C114">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C115">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -2130,21 +2130,21 @@
         <v>40</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C116">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -2152,21 +2152,21 @@
         <v>41</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>406225</v>
+      <c r="A119" t="s">
+        <v>41</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2174,26 +2174,26 @@
         <v>406225</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>606305</v>
+        <v>406225</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>656300</v>
+        <v>606305</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>1</v>
@@ -2204,29 +2204,29 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
+        <v>656300</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
         <v>656305</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C123">
+      <c r="B124" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C124">
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>42</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C124">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>726004</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>30</v>
@@ -2237,24 +2237,24 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>726003</v>
+        <v>726004</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>246030</v>
+        <v>726003</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C127">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2262,15 +2262,15 @@
         <v>246030</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C128">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>726003</v>
+        <v>246030</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>1</v>
@@ -2281,178 +2281,178 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
+        <v>726003</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
         <v>726004</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="B131" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>42</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C131">
+      <c r="B132" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C132">
         <v>60</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
         <v>761016</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C132">
+      <c r="B133" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C133">
         <v>120</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>159</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C133">
+      <c r="B134" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C134">
         <v>20</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
         <v>416269</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C134">
+      <c r="B135" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C135">
         <v>150</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>160</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C135">
-        <v>120</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C137">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C139">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C141">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C143">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C144">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C145">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -2460,7 +2460,7 @@
         <v>170</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C146">
         <v>120</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>1</v>
@@ -2479,62 +2479,62 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>1</v>
@@ -2545,7 +2545,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>1</v>
@@ -2556,51 +2556,51 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C155">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C158">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>30</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C160">
         <v>60</v>
@@ -2625,26 +2625,26 @@
         <v>46</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C161">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C162">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>1</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>1</v>
@@ -2666,13 +2666,13 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C165">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -2680,21 +2680,21 @@
         <v>47</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167">
-        <v>416274</v>
+      <c r="A167" t="s">
+        <v>47</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C167">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -2702,51 +2702,51 @@
         <v>416274</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169">
+        <v>416274</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>48</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C169">
+      <c r="B170" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C170">
         <v>150</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170">
-        <v>406320</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C170">
-        <v>120</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>416330</v>
+        <v>406320</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C171">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>406319</v>
+        <v>416330</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C172">
         <v>90</v>
@@ -2757,32 +2757,32 @@
         <v>406319</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C173">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>406323</v>
+        <v>406319</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C174">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>416251</v>
+        <v>406323</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C175">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -2790,21 +2790,21 @@
         <v>416251</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C176">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>416251</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C177">
         <v>80</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>49</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C177">
-        <v>100</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -2812,109 +2812,109 @@
         <v>49</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C178">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>50</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C180">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
         <v>51</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C180">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181">
+      <c r="B181" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C181">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
         <v>416264</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C181">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="B182" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C182">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
         <v>52</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C182">
+      <c r="B183" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C183">
         <v>110</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183">
-        <v>406255</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C183">
-        <v>100</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184">
+        <v>406255</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C184">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185">
         <v>416026</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C184">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>53</v>
-      </c>
       <c r="B185" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C185">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C186">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C187">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -2922,21 +2922,21 @@
         <v>55</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C188">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C189">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -2944,70 +2944,70 @@
         <v>57</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C190">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191">
-        <v>406215</v>
+      <c r="A191" t="s">
+        <v>57</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C191">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192">
+        <v>406215</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C192">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
         <v>406266</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C192">
+      <c r="B193" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C193">
         <v>180</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
         <v>58</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C193">
+      <c r="B194" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C194">
         <v>140</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194">
-        <v>406271</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C194">
-        <v>160</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195">
+        <v>406271</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C195">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
         <v>656330</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C195">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>59</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>1</v>
@@ -3017,30 +3017,30 @@
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197">
-        <v>406295</v>
+      <c r="A197" t="s">
+        <v>59</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C197">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>406286</v>
+        <v>406295</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C198">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>406281</v>
+        <v>406286</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>1</v>
@@ -3050,14 +3050,14 @@
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>60</v>
+      <c r="A200">
+        <v>406281</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C200">
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -3065,76 +3065,76 @@
         <v>60</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C201">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C202">
-        <v>160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C203">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C204">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>174</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C205">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
         <v>175</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C205">
+      <c r="B206" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C206">
         <v>150</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206">
-        <v>716317</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C206">
-        <v>140</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>706290</v>
+        <v>716317</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C207">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -3142,37 +3142,37 @@
         <v>706290</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C208">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>416357</v>
+        <v>706290</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C209">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>416337</v>
+        <v>416357</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C210">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>416327</v>
+        <v>416337</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>1</v>
@@ -3183,13 +3183,13 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>416272</v>
+        <v>416327</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C212">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -3197,21 +3197,21 @@
         <v>416272</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C213">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>666000</v>
+        <v>416272</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C214">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -3219,29 +3219,29 @@
         <v>666000</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C215">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>666000</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C216">
         <v>130</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>61</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C216">
-        <v>90</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C217">
         <v>90</v>
@@ -3252,21 +3252,21 @@
         <v>62</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C218">
         <v>90</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219">
-        <v>406005</v>
+      <c r="A219" t="s">
+        <v>62</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C219">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -3274,92 +3274,92 @@
         <v>406005</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C220">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>716020</v>
+        <v>406005</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C221">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222">
+        <v>716020</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C222">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223">
         <v>736323</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C222">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>63</v>
-      </c>
       <c r="B223" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C223">
         <v>120</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224">
+      <c r="A224" t="s">
+        <v>63</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C224">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225">
         <v>416112</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C224">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
+      <c r="B225" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C225">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
         <v>64</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C225">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226">
+      <c r="B226" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C226">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227">
         <v>426100</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C226">
+      <c r="B227" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C227">
         <v>80</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
         <v>64</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C227">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228">
-        <v>426100</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>1</v>
@@ -3370,18 +3370,18 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229">
+        <v>426100</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C229">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230">
         <v>416112</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C229">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>63</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>1</v>
@@ -3392,7 +3392,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>1</v>
@@ -3403,21 +3403,21 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>65</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C232">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
         <v>66</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C232">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233">
-        <v>406115</v>
-      </c>
       <c r="B233" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C233">
         <v>80</v>
@@ -3428,21 +3428,21 @@
         <v>406115</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C234">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>666001</v>
+        <v>406115</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C235">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -3450,10 +3450,10 @@
         <v>666001</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C236">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -3461,54 +3461,54 @@
         <v>666001</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C237">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>550801</v>
+        <v>666001</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C238">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239">
+        <v>550801</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C239">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240">
         <v>553424</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C239">
+      <c r="B240" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C240">
         <v>100</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>67</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C240">
-        <v>150</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C241">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -3516,18 +3516,18 @@
         <v>68</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C242">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>176</v>
+        <v>68</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C243">
         <v>90</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>69</v>
+        <v>176</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>30</v>
@@ -3546,40 +3546,40 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C245">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C246">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>71</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C247">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
         <v>72</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C247">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248">
-        <v>721015</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>30</v>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>721009</v>
+        <v>721015</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>30</v>
@@ -3601,7 +3601,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>341040</v>
+        <v>721009</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>30</v>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>341030</v>
+        <v>341040</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>30</v>
@@ -3626,15 +3626,15 @@
         <v>341030</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C252">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>341040</v>
+        <v>341030</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>1</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>721009</v>
+        <v>341040</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>1</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>721015</v>
+        <v>721009</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>1</v>
@@ -3666,8 +3666,8 @@
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>72</v>
+      <c r="A256">
+        <v>721015</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>1</v>
@@ -3689,46 +3689,46 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C258">
-        <v>110</v>
+        <v>55</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C260">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C261">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -3736,37 +3736,37 @@
         <v>74</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C262">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C263">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C264">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>30</v>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>30</v>
@@ -3787,58 +3787,58 @@
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267">
-        <v>720024</v>
+      <c r="A267" t="s">
+        <v>77</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C267">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268">
+        <v>720024</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C268">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269">
         <v>720022</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C268">
+      <c r="B269" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C269">
         <v>70</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>78</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C269">
-        <v>80</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>78</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C270">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
         <v>79</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C270">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271">
-        <v>661000</v>
-      </c>
       <c r="B271" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C271">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -3846,15 +3846,15 @@
         <v>661000</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C272">
         <v>70</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>78</v>
+      <c r="A273">
+        <v>661000</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>1</v>
@@ -3865,7 +3865,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>1</v>
@@ -3875,8 +3875,8 @@
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275">
-        <v>720022</v>
+      <c r="A275" t="s">
+        <v>79</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>1</v>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>720024</v>
+        <v>720022</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>1</v>
@@ -3897,8 +3897,8 @@
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>77</v>
+      <c r="A277">
+        <v>720024</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>1</v>
@@ -3909,46 +3909,46 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C278">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C279">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>75</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
         <v>80</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C280">
+      <c r="B281" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C281">
         <v>100</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281">
-        <v>416210</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C281">
-        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -3956,54 +3956,54 @@
         <v>416210</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>416210</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C283">
         <v>100</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
         <v>80</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C283">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284">
-        <v>406210</v>
-      </c>
       <c r="B284" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C284">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>650050</v>
+        <v>406210</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C285">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>650040</v>
+        <v>650050</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C286">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -4011,10 +4011,10 @@
         <v>650040</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C287">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -4022,21 +4022,21 @@
         <v>650040</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C288">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>650050</v>
+        <v>650040</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C289">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -4044,21 +4044,21 @@
         <v>650050</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C290">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>650020</v>
+        <v>650050</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C291">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -4066,21 +4066,21 @@
         <v>650020</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C292">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>600138</v>
+        <v>650020</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C293">
-        <v>170</v>
+        <v>100</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -4088,26 +4088,26 @@
         <v>600138</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C294">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>600121</v>
+        <v>600138</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C295">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>600127</v>
+        <v>600121</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>30</v>
@@ -4118,7 +4118,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>600227</v>
+        <v>600127</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>30</v>
@@ -4132,26 +4132,26 @@
         <v>600227</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C298">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>600127</v>
+        <v>600227</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C299">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>600121</v>
+        <v>600127</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>1</v>
@@ -4162,13 +4162,13 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>600128</v>
+        <v>600121</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C301">
-        <v>150</v>
+        <v>90</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -4176,21 +4176,21 @@
         <v>600128</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C302">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>650030</v>
+        <v>600128</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C303">
-        <v>170</v>
+        <v>70</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -4198,21 +4198,21 @@
         <v>650030</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C304">
-        <v>70</v>
+        <v>170</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>660000</v>
+        <v>650030</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C305">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -4220,21 +4220,21 @@
         <v>660000</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C306">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>660000</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C307">
         <v>80</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>82</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C307">
-        <v>110</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -4242,18 +4242,18 @@
         <v>82</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C308">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -4264,7 +4264,7 @@
         <v>83</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -4275,32 +4275,32 @@
         <v>83</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C311">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C312">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313">
-        <v>406670</v>
+      <c r="A313" t="s">
+        <v>82</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C313">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -4308,32 +4308,32 @@
         <v>406670</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C314">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315">
+        <v>406670</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316">
         <v>406316</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C315">
+      <c r="B316" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C316">
         <v>120</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>84</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C316">
-        <v>80</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -4341,21 +4341,21 @@
         <v>84</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C317">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C318">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -4363,59 +4363,59 @@
         <v>85</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C319">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
+        <v>85</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
         <v>86</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C320">
+      <c r="B321" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C321">
         <v>60</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322">
         <v>550800</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C321">
+      <c r="B322" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C322">
         <v>80</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
-        <v>87</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C322">
-        <v>90</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C323">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>30</v>
@@ -4426,18 +4426,18 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C325">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>30</v>
@@ -4448,73 +4448,73 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C327">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>92</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C328">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
         <v>93</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C328">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329">
+      <c r="B329" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330">
         <v>720023</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C329">
+      <c r="B330" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C330">
         <v>80</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
         <v>94</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C330">
+      <c r="B331" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C331">
         <v>70</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331">
-        <v>240040</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C331">
-        <v>60</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>240030</v>
+        <v>240040</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C332">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>240020</v>
+        <v>240030</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>30</v>
@@ -4528,26 +4528,26 @@
         <v>240020</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C334">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>240030</v>
+        <v>240020</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C335">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>240040</v>
+        <v>240030</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>1</v>
@@ -4557,8 +4557,8 @@
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>94</v>
+      <c r="A337">
+        <v>240040</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>1</v>
@@ -4568,19 +4568,19 @@
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338">
+      <c r="A338" t="s">
+        <v>94</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C338">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339">
         <v>720023</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C338">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
-        <v>93</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>1</v>
@@ -4591,40 +4591,40 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C340">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C341">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C342">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>1</v>
@@ -4635,18 +4635,18 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C344">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>1</v>
@@ -4657,35 +4657,35 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C346">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C347">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C348">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -4693,15 +4693,15 @@
         <v>97</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C349">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>1</v>
@@ -4712,40 +4712,40 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
+        <v>96</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C351">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
         <v>95</v>
       </c>
-      <c r="B351" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C351">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A352">
-        <v>722010</v>
-      </c>
       <c r="B352" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C352">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>722005</v>
+        <v>722010</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>722006</v>
+        <v>722005</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>30</v>
@@ -4756,13 +4756,13 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>722000</v>
+        <v>722006</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C355">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -4770,7 +4770,7 @@
         <v>722000</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C356">
         <v>60</v>
@@ -4778,18 +4778,18 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>722006</v>
+        <v>722000</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C357">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>722005</v>
+        <v>722006</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>1</v>
@@ -4800,40 +4800,40 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359">
+        <v>722005</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360">
         <v>722010</v>
       </c>
-      <c r="B359" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C359">
+      <c r="B360" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C360">
         <v>50</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A360" t="s">
-        <v>98</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C360">
-        <v>80</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C361">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>30</v>
@@ -4844,13 +4844,13 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C363">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -4858,7 +4858,7 @@
         <v>101</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C364">
         <v>60</v>
@@ -4866,29 +4866,29 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C365">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C366">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>1</v>
@@ -4899,40 +4899,40 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C368">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C369">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C370">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>30</v>
@@ -4946,26 +4946,26 @@
         <v>105</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C372">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C373">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>1</v>
@@ -4976,35 +4976,35 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C375">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C376">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C377">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -5012,70 +5012,70 @@
         <v>107</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C378">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
+        <v>107</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C379">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
         <v>106</v>
       </c>
-      <c r="B379" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C379">
+      <c r="B380" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C380">
         <v>60</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A380">
-        <v>406010</v>
-      </c>
-      <c r="B380" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C380">
-        <v>120</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
-        <v>406321</v>
+        <v>406010</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C381">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382">
-        <v>406660</v>
+        <v>406321</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C382">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383">
-        <v>406329</v>
+        <v>406660</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C383">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384">
-        <v>406325</v>
+        <v>406329</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>1</v>
@@ -5086,13 +5086,13 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385">
-        <v>416240</v>
+        <v>406325</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C385">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -5100,15 +5100,15 @@
         <v>416240</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C386">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
-        <v>108</v>
+      <c r="A387">
+        <v>416240</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>1</v>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C388">
         <v>100</v>
@@ -5133,21 +5133,21 @@
         <v>109</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C389">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C390">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -5155,7 +5155,7 @@
         <v>110</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C391">
         <v>100</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C392">
         <v>100</v>
@@ -5177,18 +5177,18 @@
         <v>111</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C393">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C394">
         <v>90</v>
@@ -5199,21 +5199,21 @@
         <v>112</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C395">
-        <v>130</v>
+        <v>90</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C396">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -5221,21 +5221,21 @@
         <v>113</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C397">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>113</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C398">
         <v>130</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A398">
-        <v>242320</v>
-      </c>
-      <c r="B398" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C398">
-        <v>100</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -5243,7 +5243,7 @@
         <v>242320</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C399">
         <v>100</v>
@@ -5251,13 +5251,13 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400">
-        <v>651050</v>
+        <v>242320</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C400">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -5265,7 +5265,7 @@
         <v>651050</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C401">
         <v>110</v>
@@ -5273,13 +5273,13 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402">
-        <v>730010</v>
+        <v>651050</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C402">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -5287,7 +5287,7 @@
         <v>730010</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C403">
         <v>100</v>
@@ -5295,10 +5295,10 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404">
-        <v>731020</v>
+        <v>730010</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C404">
         <v>100</v>
@@ -5309,21 +5309,21 @@
         <v>731020</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C405">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406">
-        <v>476273</v>
+        <v>731020</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C406">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -5331,21 +5331,21 @@
         <v>476273</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C407">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A408" t="s">
-        <v>114</v>
+      <c r="A408">
+        <v>476273</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C408">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -5353,21 +5353,21 @@
         <v>114</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C409">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410">
-        <v>466009</v>
+      <c r="A410" t="s">
+        <v>114</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C410">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -5375,21 +5375,21 @@
         <v>466009</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C411">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412">
-        <v>416273</v>
+        <v>466009</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C412">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -5397,21 +5397,21 @@
         <v>416273</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C413">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414">
-        <v>466023</v>
+        <v>416273</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C414">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -5419,21 +5419,21 @@
         <v>466023</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C415">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416">
-        <v>426200</v>
+        <v>466023</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C416">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -5441,21 +5441,21 @@
         <v>426200</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C417">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418">
-        <v>406272</v>
+        <v>426200</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C418">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -5463,21 +5463,21 @@
         <v>406272</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C419">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>115</v>
+      <c r="A420">
+        <v>406272</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C420">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -5485,18 +5485,18 @@
         <v>115</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C421">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C422">
         <v>80</v>
@@ -5507,7 +5507,7 @@
         <v>116</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C423">
         <v>80</v>
@@ -5515,10 +5515,10 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C424">
         <v>80</v>
@@ -5529,147 +5529,147 @@
         <v>117</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C425">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A426">
-        <v>416338</v>
+      <c r="A426" t="s">
+        <v>117</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C426">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>416331</v>
+        <v>416338</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C427">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>416065</v>
+        <v>416331</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C428">
-        <v>90</v>
+        <v>200</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>416067</v>
+        <v>416065</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C429">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>416086</v>
+        <v>416067</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C430">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431">
+        <v>416086</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C431">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432">
         <v>416096</v>
       </c>
-      <c r="B431" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C431">
+      <c r="B432" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C432">
         <v>120</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A432" t="s">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
         <v>118</v>
       </c>
-      <c r="B432" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C432">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433">
-        <v>666003</v>
-      </c>
       <c r="B433" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C433">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434">
+        <v>666003</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C434">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435">
         <v>666002</v>
       </c>
-      <c r="B434" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C434">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A435" t="s">
+      <c r="B435" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C435">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
         <v>119</v>
       </c>
-      <c r="B435" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C435">
+      <c r="B436" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C436">
         <v>85</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A436">
-        <v>416070</v>
-      </c>
-      <c r="B436" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C436">
-        <v>90</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437">
+        <v>416070</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C437">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438">
         <v>416069</v>
-      </c>
-      <c r="B437" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C437">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
-        <v>120</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>1</v>
@@ -5679,8 +5679,8 @@
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A439">
-        <v>406340</v>
+      <c r="A439" t="s">
+        <v>120</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>1</v>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>416301</v>
+        <v>406340</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>1</v>
@@ -5702,35 +5702,35 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>416119</v>
+        <v>416301</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C441">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>406081</v>
+        <v>416119</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C442">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>416068</v>
+        <v>406081</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C443">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -5738,48 +5738,48 @@
         <v>416068</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C444">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>736315</v>
+        <v>416068</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C445">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446">
+        <v>736315</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C446">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447">
         <v>736334</v>
       </c>
-      <c r="B446" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C446">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
+      <c r="B447" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C447">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
         <v>121</v>
-      </c>
-      <c r="B447" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C447">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A448">
-        <v>406307</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>1</v>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>466400</v>
+        <v>406307</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>1</v>
@@ -5801,13 +5801,13 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>416139</v>
+        <v>466400</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C450">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -5815,7 +5815,7 @@
         <v>416139</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C451">
         <v>80</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452">
-        <v>416148</v>
+        <v>416139</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>1</v>
@@ -5833,30 +5833,30 @@
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A453" t="s">
-        <v>122</v>
+      <c r="A453">
+        <v>416148</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C453">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C454">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>1</v>
@@ -5867,7 +5867,7 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>1</v>
@@ -5878,40 +5878,40 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C457">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C458">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C459">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>1</v>
@@ -5921,30 +5921,30 @@
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A461">
+      <c r="A461" t="s">
+        <v>171</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C461">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462">
         <v>406310</v>
       </c>
-      <c r="B461" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C461">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462" t="s">
+      <c r="B462" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C462">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
         <v>129</v>
-      </c>
-      <c r="B462" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C462">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A463">
-        <v>416180</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>1</v>
@@ -5955,7 +5955,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
-        <v>606180</v>
+        <v>416180</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>1</v>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
-        <v>656310</v>
+        <v>606180</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>1</v>
@@ -5977,7 +5977,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466">
-        <v>416311</v>
+        <v>656310</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>1</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467">
-        <v>406157</v>
+        <v>416311</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>1</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468">
-        <v>416182</v>
+        <v>406157</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>1</v>
@@ -6010,18 +6010,18 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469">
-        <v>406315</v>
+        <v>416182</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C469">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470">
-        <v>406312</v>
+        <v>406315</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>1</v>
@@ -6031,19 +6031,19 @@
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A471" t="s">
-        <v>130</v>
+      <c r="A471">
+        <v>406312</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C471">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>30</v>
@@ -6057,15 +6057,15 @@
         <v>131</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C473">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>1</v>
@@ -6075,14 +6075,14 @@
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A475">
-        <v>762013</v>
+      <c r="A475" t="s">
+        <v>130</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C475">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -6090,21 +6090,21 @@
         <v>762013</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C476">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>762013</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C477">
         <v>60</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A477" t="s">
-        <v>132</v>
-      </c>
-      <c r="B477" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C477">
-        <v>90</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -6112,21 +6112,21 @@
         <v>132</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C478">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C479">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -6134,21 +6134,21 @@
         <v>133</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C480">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C481">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -6156,21 +6156,21 @@
         <v>134</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C482">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>134</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C483">
         <v>60</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A483">
-        <v>242020</v>
-      </c>
-      <c r="B483" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C483">
-        <v>70</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -6178,21 +6178,21 @@
         <v>242020</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C484">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485">
-        <v>602010</v>
+        <v>242020</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C485">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -6200,21 +6200,21 @@
         <v>602010</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C486">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487">
-        <v>652010</v>
+        <v>602010</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C487">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -6222,37 +6222,37 @@
         <v>652010</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C488">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489">
+        <v>652010</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C489">
         <v>60</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
-        <v>135</v>
-      </c>
-      <c r="B489" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C489">
-        <v>70</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C490">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>1</v>
@@ -6263,7 +6263,7 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>1</v>
@@ -6274,29 +6274,29 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C493">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C494">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>56</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>56</v>
@@ -6321,26 +6321,26 @@
         <v>138</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C497">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C498">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>30</v>
@@ -6351,7 +6351,7 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>30</v>
@@ -6362,29 +6362,29 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C501">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C502">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>1</v>
@@ -6395,29 +6395,29 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C504">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C505">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>56</v>
@@ -6431,26 +6431,26 @@
         <v>141</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C507">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C508">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>30</v>
@@ -6461,13 +6461,13 @@
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C510">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -6475,10 +6475,10 @@
         <v>142</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C511">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -6486,18 +6486,18 @@
         <v>142</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C512">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A513">
-        <v>720004</v>
+      <c r="A513" t="s">
+        <v>142</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C513">
         <v>70</v>
@@ -6505,21 +6505,21 @@
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B514" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C514">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515">
-        <v>720004</v>
+        <v>720003</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C515">
         <v>0</v>
@@ -6527,7 +6527,7 @@
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>30</v>
@@ -6541,7 +6541,7 @@
         <v>720003</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C517">
         <v>0</v>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518">
-        <v>720004</v>
+        <v>720003</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>1</v>
@@ -6560,13 +6560,13 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519">
-        <v>721001</v>
+        <v>720004</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C519">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -6574,10 +6574,10 @@
         <v>721001</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C520">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -6585,7 +6585,7 @@
         <v>721001</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C521">
         <v>0</v>
@@ -6593,13 +6593,13 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522">
-        <v>651030</v>
+        <v>721001</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C522">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -6607,21 +6607,21 @@
         <v>651030</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C523">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524">
-        <v>651010</v>
+        <v>651030</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C524">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -6629,37 +6629,37 @@
         <v>651010</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C525">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A526" t="s">
-        <v>143</v>
+      <c r="A526">
+        <v>651010</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C526">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C527">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>1</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>1</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C530">
         <v>0</v>
@@ -6692,7 +6692,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>56</v>
@@ -6703,7 +6703,7 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>56</v>
@@ -6714,7 +6714,7 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>56</v>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C534">
         <v>0</v>
@@ -6736,7 +6736,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>30</v>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>30</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>30</v>
@@ -6769,32 +6769,32 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C538">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C539">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C540">
         <v>0</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>56</v>
@@ -6813,10 +6813,10 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C542">
         <v>0</v>
@@ -6824,7 +6824,7 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>30</v>
@@ -6835,24 +6835,24 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C544">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B545" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C545">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -6860,32 +6860,32 @@
         <v>150</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C546">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C547">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C548">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -6893,18 +6893,18 @@
         <v>151</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C549">
-        <v>110</v>
+        <v>150</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A550">
-        <v>721014</v>
+      <c r="A550" t="s">
+        <v>151</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C550">
         <v>110</v>
@@ -6912,24 +6912,24 @@
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551">
-        <v>721008</v>
+        <v>721014</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C551">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552">
-        <v>721005</v>
+        <v>721008</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C552">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -6937,15 +6937,15 @@
         <v>721005</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C553">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554">
-        <v>721008</v>
+        <v>721005</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>1</v>
@@ -6956,24 +6956,24 @@
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555">
+        <v>721008</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C555">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A556">
         <v>721014</v>
       </c>
-      <c r="B555" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C555">
+      <c r="B556" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C556">
         <v>50</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A556" t="s">
-        <v>152</v>
-      </c>
-      <c r="B556" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C556">
-        <v>110</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -6981,32 +6981,32 @@
         <v>152</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C557">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>152</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C558">
         <v>60</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A558">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A559">
         <v>241040</v>
       </c>
-      <c r="B558" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C558">
+      <c r="B559" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C559">
         <v>120</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A559">
-        <v>241020</v>
-      </c>
-      <c r="B559" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C559">
-        <v>70</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7014,43 +7014,43 @@
         <v>241020</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C560">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561">
-        <v>241040</v>
+        <v>241020</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C561">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562">
-        <v>601138</v>
+        <v>241040</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C562">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563">
-        <v>601128</v>
+        <v>601138</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C563">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7058,54 +7058,54 @@
         <v>601128</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C564">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565">
+        <v>601128</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C565">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A566">
         <v>601138</v>
       </c>
-      <c r="B565" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C565">
+      <c r="B566" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C566">
         <v>60</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A566" t="s">
-        <v>153</v>
-      </c>
-      <c r="B566" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C566">
-        <v>120</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B567" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C567">
-        <v>70</v>
+        <v>120</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B568" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C568">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7113,31 +7113,42 @@
         <v>155</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C569">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B570" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C570">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
+        <v>154</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
         <v>153</v>
       </c>
-      <c r="B571" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C571">
+      <c r="B572" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C572">
         <v>50</v>
       </c>
     </row>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E54640-831E-41BC-A3ED-7FFD86ECDBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E87D85B-1814-4175-B9A0-F3CB796D2D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="178">
   <si>
     <t>GP8280</t>
   </si>
@@ -567,6 +567,9 @@
   </si>
   <si>
     <t>P29537</t>
+  </si>
+  <si>
+    <t>GO2220</t>
   </si>
 </sst>
 </file>
@@ -851,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C572"/>
+  <dimension ref="A1:C575"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -3109,7 +3112,7 @@
         <v>174</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -3117,35 +3120,35 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>174</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
         <v>175</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C206">
+      <c r="B207" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C207">
         <v>150</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207">
-        <v>716317</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C207">
-        <v>140</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>706290</v>
+        <v>716317</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C208">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -3153,37 +3156,37 @@
         <v>706290</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C209">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>416357</v>
+        <v>706290</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C210">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>416337</v>
+        <v>416357</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C211">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>416327</v>
+        <v>416337</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>1</v>
@@ -3194,186 +3197,186 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>416272</v>
+        <v>416327</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C213">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>416272</v>
+        <v>416302</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C214">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215">
-        <v>666000</v>
+      <c r="A215" t="s">
+        <v>177</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C215">
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216">
+        <v>416272</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C216">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>416272</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C217">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218">
         <v>666000</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C216">
+      <c r="B218" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C218">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>666000</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C219">
         <v>130</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
         <v>61</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C217">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+      <c r="B220" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C220">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
         <v>62</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C218">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+      <c r="B221" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C221">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
         <v>62</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C219">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220">
-        <v>406005</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C220">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221">
-        <v>406005</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C221">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222">
-        <v>716020</v>
-      </c>
       <c r="B222" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C222">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>736323</v>
+        <v>406005</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C223">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>63</v>
+      <c r="A224">
+        <v>406005</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C224">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225">
+        <v>716020</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C225">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>736323</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C226">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>63</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C227">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228">
         <v>416112</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C225">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+      <c r="B228" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C228">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
         <v>64</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C226">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227">
-        <v>426100</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C227">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>64</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C228">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229">
-        <v>426100</v>
-      </c>
       <c r="B229" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C229">
         <v>90</v>
@@ -3381,194 +3384,194 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>416112</v>
+        <v>426100</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C230">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>64</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C231">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>426100</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C232">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>416112</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C233">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
         <v>63</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C231">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
+      <c r="B234" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C234">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
         <v>65</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C232">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
+      <c r="B235" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C235">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
         <v>66</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C233">
+      <c r="B236" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C236">
         <v>80</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234">
-        <v>406115</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C234">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235">
-        <v>406115</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C235">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236">
-        <v>666001</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C236">
-        <v>120</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>666001</v>
+        <v>406115</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C237">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>666001</v>
+        <v>406115</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C238">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>550801</v>
+        <v>666001</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C239">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240">
+        <v>666001</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C240">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>666001</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C241">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>550801</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C242">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243">
         <v>553424</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C240">
+      <c r="B243" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C243">
         <v>100</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>67</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C241">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>68</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C242">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>68</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C243">
-        <v>90</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C244">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C245">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C246">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>30</v>
@@ -3579,18 +3582,18 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C248">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249">
-        <v>721015</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>30</v>
@@ -3600,19 +3603,19 @@
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250">
-        <v>721009</v>
+      <c r="A250" t="s">
+        <v>71</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C250">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251">
-        <v>341040</v>
+      <c r="A251" t="s">
+        <v>72</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>30</v>
@@ -3623,7 +3626,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>341030</v>
+        <v>721015</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>30</v>
@@ -3634,13 +3637,13 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>341030</v>
+        <v>721009</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C253">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -3648,26 +3651,26 @@
         <v>341040</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C254">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>721009</v>
+        <v>341030</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C255">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>721015</v>
+        <v>341030</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>1</v>
@@ -3677,8 +3680,8 @@
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>72</v>
+      <c r="A257">
+        <v>341040</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>1</v>
@@ -3688,8 +3691,8 @@
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>71</v>
+      <c r="A258">
+        <v>721009</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>1</v>
@@ -3699,58 +3702,58 @@
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>70</v>
+      <c r="A259">
+        <v>721015</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C259">
-        <v>110</v>
+        <v>55</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C261">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C262">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C263">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -3758,59 +3761,59 @@
         <v>73</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C264">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C265">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C266">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C267">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>75</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C268">
         <v>70</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268">
-        <v>720024</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C268">
-        <v>90</v>
-      </c>
-    </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269">
-        <v>720022</v>
+      <c r="A269" t="s">
+        <v>76</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>30</v>
@@ -3821,18 +3824,18 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C270">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>79</v>
+      <c r="A271">
+        <v>720024</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>30</v>
@@ -3843,7 +3846,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>661000</v>
+        <v>720022</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>30</v>
@@ -3853,33 +3856,33 @@
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273">
-        <v>661000</v>
+      <c r="A273" t="s">
+        <v>78</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C273">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C274">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>79</v>
+      <c r="A275">
+        <v>661000</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C275">
         <v>70</v>
@@ -3887,7 +3890,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>720022</v>
+        <v>661000</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>1</v>
@@ -3897,8 +3900,8 @@
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277">
-        <v>720024</v>
+      <c r="A277" t="s">
+        <v>78</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>1</v>
@@ -3909,7 +3912,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>1</v>
@@ -3919,58 +3922,58 @@
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>76</v>
+      <c r="A279">
+        <v>720022</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C279">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>75</v>
+      <c r="A280">
+        <v>720024</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C280">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C281">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282">
-        <v>416210</v>
+      <c r="A282" t="s">
+        <v>76</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C282">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283">
-        <v>416210</v>
+      <c r="A283" t="s">
+        <v>75</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C283">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -3978,175 +3981,175 @@
         <v>80</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C284">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>406210</v>
+        <v>416210</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C285">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>650050</v>
+        <v>416210</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C286">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287">
-        <v>650040</v>
+      <c r="A287" t="s">
+        <v>80</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C287">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>650040</v>
+        <v>406210</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C288">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>650040</v>
+        <v>650050</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="C289">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>650050</v>
+        <v>650040</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C290">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>650050</v>
+        <v>650040</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C291">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>650020</v>
+        <v>650040</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C292">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>650020</v>
+        <v>650050</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C293">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>600138</v>
+        <v>650050</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C294">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>600138</v>
+        <v>650020</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C295">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>600121</v>
+        <v>650020</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C296">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>600127</v>
+        <v>600138</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C297">
-        <v>140</v>
+        <v>170</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>600227</v>
+        <v>600138</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C298">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>600227</v>
+        <v>600121</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C299">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -4154,29 +4157,29 @@
         <v>600127</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C300">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>600121</v>
+        <v>600227</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C301">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>600128</v>
+        <v>600227</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C302">
         <v>150</v>
@@ -4184,282 +4187,282 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>600128</v>
+        <v>600127</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C303">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>650030</v>
+        <v>600121</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C304">
-        <v>170</v>
+        <v>90</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>650030</v>
+        <v>600128</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C305">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>660000</v>
+        <v>600128</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C306">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307">
+        <v>650030</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C307">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>650030</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C308">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309">
         <v>660000</v>
       </c>
-      <c r="B307" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C307">
+      <c r="B309" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C309">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>660000</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C310">
         <v>80</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>82</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C308">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>82</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C309">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>83</v>
-      </c>
-      <c r="B310" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C310">
-        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C311">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C312">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
+        <v>83</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>83</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>83</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C315">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
         <v>82</v>
       </c>
-      <c r="B313" s="1" t="s">
+      <c r="B316" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C313">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314">
+      <c r="C316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317">
         <v>406670</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C314">
+      <c r="B317" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C317">
         <v>110</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318">
         <v>406670</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C315">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316">
+      <c r="B318" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319">
         <v>406316</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C316">
+      <c r="B319" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C319">
         <v>120</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>84</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C317">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>84</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C318">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>85</v>
-      </c>
-      <c r="B319" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C319">
-        <v>60</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C320">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>85</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C322">
         <v>60</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322">
-        <v>550800</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C322">
-        <v>80</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C323">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C324">
         <v>60</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>89</v>
+      <c r="A325">
+        <v>550800</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C325">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C326">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C327">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>30</v>
@@ -4470,7 +4473,7 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>30</v>
@@ -4480,66 +4483,66 @@
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330">
-        <v>720023</v>
+      <c r="A330" t="s">
+        <v>91</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C330">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C331">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332">
-        <v>240040</v>
+      <c r="A332" t="s">
+        <v>93</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C332">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>240030</v>
+        <v>720023</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C333">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334">
-        <v>240020</v>
+      <c r="A334" t="s">
+        <v>94</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C334">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>240020</v>
+        <v>240040</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C335">
         <v>60</v>
@@ -4550,7 +4553,7 @@
         <v>240030</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C336">
         <v>50</v>
@@ -4558,84 +4561,84 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>240040</v>
+        <v>240020</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C337">
         <v>50</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>94</v>
+      <c r="A338">
+        <v>240020</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C338">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>720023</v>
+        <v>240030</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C339">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
-        <v>93</v>
+      <c r="A340">
+        <v>240040</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C340">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C341">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>91</v>
+      <c r="A342">
+        <v>720023</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C342">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C343">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>1</v>
@@ -4646,7 +4649,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>1</v>
@@ -4657,57 +4660,57 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C346">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C347">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C348">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C349">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C350">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -4715,76 +4718,76 @@
         <v>96</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C351">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
+        <v>97</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C352">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>97</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C353">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>96</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C354">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
         <v>95</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C352">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A353">
-        <v>722010</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C353">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A354">
-        <v>722005</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C354">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355">
-        <v>722006</v>
-      </c>
       <c r="B355" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C355">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>722000</v>
+        <v>722010</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C356">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>722000</v>
+        <v>722005</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C357">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -4792,7 +4795,7 @@
         <v>722006</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -4800,79 +4803,79 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>722005</v>
+        <v>722000</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C359">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360">
+        <v>722000</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C360">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>722006</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>722005</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363">
         <v>722010</v>
       </c>
-      <c r="B360" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C360">
+      <c r="B363" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C363">
         <v>50</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A361" t="s">
-        <v>98</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C361">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A362" t="s">
-        <v>99</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C362">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A363" t="s">
-        <v>100</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C363">
-        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C364">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C365">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -4880,62 +4883,62 @@
         <v>100</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C366">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C367">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C368">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C369">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C370">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -4943,24 +4946,24 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C372">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C373">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -4968,7 +4971,7 @@
         <v>104</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -4976,10 +4979,10 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -4987,7 +4990,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>1</v>
@@ -4998,29 +5001,29 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C377">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C378">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>1</v>
@@ -5034,59 +5037,59 @@
         <v>106</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C380">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>107</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C381">
         <v>60</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A381">
-        <v>406010</v>
-      </c>
-      <c r="B381" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C381">
-        <v>120</v>
-      </c>
-    </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A382">
-        <v>406321</v>
+      <c r="A382" t="s">
+        <v>107</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C382">
-        <v>150</v>
+        <v>70</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A383">
-        <v>406660</v>
+      <c r="A383" t="s">
+        <v>106</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C383">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384">
-        <v>406329</v>
+        <v>406010</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C384">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385">
-        <v>406325</v>
+        <v>406321</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>1</v>
@@ -5097,10 +5100,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386">
-        <v>416240</v>
+        <v>406660</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C386">
         <v>120</v>
@@ -5108,54 +5111,54 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387">
+        <v>406329</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C387">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>406325</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C388">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389">
         <v>416240</v>
       </c>
-      <c r="B387" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C387">
+      <c r="B389" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C389">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>416240</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C390">
         <v>100</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
-        <v>108</v>
-      </c>
-      <c r="B388" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C388">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
-        <v>109</v>
-      </c>
-      <c r="B389" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C389">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
-        <v>109</v>
-      </c>
-      <c r="B390" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C390">
-        <v>120</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C391">
         <v>100</v>
@@ -5163,10 +5166,10 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C392">
         <v>100</v>
@@ -5174,120 +5177,120 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C393">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C394">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C395">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C396">
-        <v>130</v>
+        <v>100</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C397">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
+        <v>112</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C398">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>112</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C399">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
         <v>113</v>
       </c>
-      <c r="B398" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C398">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A399">
-        <v>242320</v>
-      </c>
-      <c r="B399" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C399">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A400">
-        <v>242320</v>
-      </c>
       <c r="B400" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C400">
         <v>100</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A401">
-        <v>651050</v>
+      <c r="A401" t="s">
+        <v>113</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C401">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402">
-        <v>651050</v>
+        <v>242320</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C402">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403">
-        <v>730010</v>
+        <v>242320</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C403">
         <v>100</v>
@@ -5295,241 +5298,241 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404">
-        <v>730010</v>
+        <v>651050</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C404">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405">
-        <v>731020</v>
+        <v>651050</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C405">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406">
-        <v>731020</v>
+        <v>730010</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C406">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407">
-        <v>476273</v>
+        <v>730010</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C407">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408">
+        <v>731020</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C408">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>731020</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C409">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410">
         <v>476273</v>
       </c>
-      <c r="B408" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C408">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A409" t="s">
-        <v>114</v>
-      </c>
-      <c r="B409" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C409">
+      <c r="B410" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C410">
         <v>60</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
-        <v>114</v>
-      </c>
-      <c r="B410" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C410">
-        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411">
-        <v>466009</v>
+        <v>476273</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>114</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C412">
         <v>60</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412">
-        <v>466009</v>
-      </c>
-      <c r="B412" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C412">
-        <v>0</v>
-      </c>
-    </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A413">
-        <v>416273</v>
+      <c r="A413" t="s">
+        <v>114</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C413">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414">
-        <v>416273</v>
+        <v>466009</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C414">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415">
-        <v>466023</v>
+        <v>466009</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C415">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416">
-        <v>466023</v>
+        <v>416273</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C416">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417">
-        <v>426200</v>
+        <v>416273</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C417">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418">
-        <v>426200</v>
+        <v>466023</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C418">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419">
-        <v>406272</v>
+        <v>466023</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C419">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420">
+        <v>426200</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C420">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>426200</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422">
         <v>406272</v>
       </c>
-      <c r="B420" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C420">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
-        <v>115</v>
-      </c>
-      <c r="B421" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C421">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
-        <v>115</v>
-      </c>
       <c r="B422" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C422">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
-        <v>116</v>
+      <c r="A423">
+        <v>406272</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C423">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C424">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C425">
         <v>80</v>
@@ -5537,172 +5540,172 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
+        <v>116</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C426">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>116</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C427">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
         <v>117</v>
       </c>
-      <c r="B426" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C426">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A427">
-        <v>416338</v>
-      </c>
-      <c r="B427" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C427">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A428">
-        <v>416331</v>
-      </c>
       <c r="B428" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C428">
-        <v>200</v>
+        <v>80</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A429">
-        <v>416065</v>
+      <c r="A429" t="s">
+        <v>117</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C429">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>416067</v>
+        <v>416338</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C430">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>416086</v>
+        <v>416331</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C431">
-        <v>90</v>
+        <v>200</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>416096</v>
+        <v>416065</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C432">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>416067</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C433">
         <v>120</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433" t="s">
-        <v>118</v>
-      </c>
-      <c r="B433" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C433">
-        <v>90</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>666003</v>
+        <v>416086</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C434">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>666002</v>
+        <v>416096</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C435">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C436">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>416070</v>
+        <v>666003</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C437">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>416069</v>
+        <v>666002</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C438">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C439">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>406340</v>
+        <v>416070</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C440">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>416301</v>
+        <v>416069</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>1</v>
@@ -5712,19 +5715,19 @@
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A442">
-        <v>416119</v>
+      <c r="A442" t="s">
+        <v>120</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C442">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>406081</v>
+        <v>406340</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>1</v>
@@ -5735,62 +5738,62 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>416068</v>
+        <v>416301</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C444">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>416068</v>
+        <v>416119</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C445">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>736315</v>
+        <v>406081</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C446">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>736334</v>
+        <v>416068</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C447">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
-        <v>121</v>
+      <c r="A448">
+        <v>416068</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C448">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>406307</v>
+        <v>736315</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>1</v>
@@ -5801,7 +5804,7 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>466400</v>
+        <v>736334</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>1</v>
@@ -5811,118 +5814,118 @@
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A451">
-        <v>416139</v>
+      <c r="A451" t="s">
+        <v>121</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C451">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452">
-        <v>416139</v>
+        <v>406307</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C452">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453">
+        <v>466400</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C453">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>416139</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C454">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>416139</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C455">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456">
         <v>416148</v>
       </c>
-      <c r="B453" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C453">
+      <c r="B456" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C456">
         <v>80</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A454" t="s">
-        <v>122</v>
-      </c>
-      <c r="B454" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C454">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A455" t="s">
-        <v>123</v>
-      </c>
-      <c r="B455" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C455">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
-        <v>124</v>
-      </c>
-      <c r="B456" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C456">
-        <v>100</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C457">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C458">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C459">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C460">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>1</v>
@@ -5932,8 +5935,8 @@
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462">
-        <v>406310</v>
+      <c r="A462" t="s">
+        <v>127</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>1</v>
@@ -5944,7 +5947,7 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>1</v>
@@ -5954,8 +5957,8 @@
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A464">
-        <v>416180</v>
+      <c r="A464" t="s">
+        <v>171</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>1</v>
@@ -5966,18 +5969,18 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
-        <v>606180</v>
+        <v>406310</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C465">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466">
-        <v>656310</v>
+      <c r="A466" t="s">
+        <v>129</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>1</v>
@@ -5988,7 +5991,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467">
-        <v>416311</v>
+        <v>416180</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>1</v>
@@ -5999,7 +6002,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468">
-        <v>406157</v>
+        <v>606180</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>1</v>
@@ -6010,7 +6013,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469">
-        <v>416182</v>
+        <v>656310</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>1</v>
@@ -6021,57 +6024,57 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470">
-        <v>406315</v>
+        <v>416311</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C470">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471">
+        <v>406157</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C471">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>416182</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C472">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>406315</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C473">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474">
         <v>406312</v>
       </c>
-      <c r="B471" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C471">
+      <c r="B474" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C474">
         <v>100</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A472" t="s">
-        <v>130</v>
-      </c>
-      <c r="B472" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C472">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A473" t="s">
-        <v>131</v>
-      </c>
-      <c r="B473" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C473">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A474" t="s">
-        <v>131</v>
-      </c>
-      <c r="B474" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C474">
-        <v>70</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -6079,227 +6082,227 @@
         <v>130</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C475">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>131</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C476">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>131</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C477">
         <v>70</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A476">
-        <v>762013</v>
-      </c>
-      <c r="B476" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C476">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A477">
-        <v>762013</v>
-      </c>
-      <c r="B477" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C477">
-        <v>60</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C478">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A479" t="s">
-        <v>132</v>
+      <c r="A479">
+        <v>762013</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C479">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>762013</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C480">
         <v>60</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A480" t="s">
-        <v>133</v>
-      </c>
-      <c r="B480" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C480">
-        <v>90</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C481">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C482">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
+        <v>133</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C483">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>133</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C484">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
         <v>134</v>
       </c>
-      <c r="B483" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C483">
+      <c r="B485" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C485">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>134</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C486">
         <v>60</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A484">
-        <v>242020</v>
-      </c>
-      <c r="B484" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C484">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A485">
-        <v>242020</v>
-      </c>
-      <c r="B485" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C485">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A486">
-        <v>602010</v>
-      </c>
-      <c r="B486" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C486">
-        <v>80</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487">
-        <v>602010</v>
+        <v>242020</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C487">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488">
-        <v>652010</v>
+        <v>242020</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C488">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489">
+        <v>602010</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C489">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490">
+        <v>602010</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C490">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491">
         <v>652010</v>
       </c>
-      <c r="B489" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C489">
+      <c r="B491" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C491">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492">
+        <v>652010</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C492">
         <v>60</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
-        <v>135</v>
-      </c>
-      <c r="B490" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C490">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A491" t="s">
-        <v>136</v>
-      </c>
-      <c r="B491" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C491">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A492" t="s">
-        <v>137</v>
-      </c>
-      <c r="B492" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C492">
-        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C493">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C494">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C495">
         <v>0</v>
@@ -6307,10 +6310,10 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C496">
         <v>0</v>
@@ -6318,24 +6321,24 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C497">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C498">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -6343,7 +6346,7 @@
         <v>137</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C499">
         <v>0</v>
@@ -6351,10 +6354,10 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C500">
         <v>0</v>
@@ -6362,32 +6365,32 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C501">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C502">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C503">
         <v>0</v>
@@ -6395,10 +6398,10 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C504">
         <v>0</v>
@@ -6409,7 +6412,7 @@
         <v>139</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C505">
         <v>70</v>
@@ -6420,7 +6423,7 @@
         <v>140</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C506">
         <v>0</v>
@@ -6431,7 +6434,7 @@
         <v>141</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C507">
         <v>0</v>
@@ -6439,10 +6442,10 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C508">
         <v>70</v>
@@ -6453,7 +6456,7 @@
         <v>140</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C509">
         <v>0</v>
@@ -6461,10 +6464,10 @@
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C510">
         <v>0</v>
@@ -6472,10 +6475,10 @@
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C511">
         <v>70</v>
@@ -6483,10 +6486,10 @@
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C512">
         <v>0</v>
@@ -6494,29 +6497,29 @@
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
+        <v>139</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
         <v>142</v>
       </c>
-      <c r="B513" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C513">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A514">
-        <v>720004</v>
-      </c>
       <c r="B514" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C514">
         <v>70</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A515">
-        <v>720003</v>
+      <c r="A515" t="s">
+        <v>142</v>
       </c>
       <c r="B515" s="1" t="s">
         <v>56</v>
@@ -6526,25 +6529,25 @@
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A516">
-        <v>720004</v>
+      <c r="A516" t="s">
+        <v>142</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C516">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>720003</v>
+        <v>720004</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C517">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -6552,7 +6555,7 @@
         <v>720003</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C518">
         <v>0</v>
@@ -6563,7 +6566,7 @@
         <v>720004</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C519">
         <v>0</v>
@@ -6571,21 +6574,21 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520">
-        <v>721001</v>
+        <v>720003</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C520">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521">
-        <v>721001</v>
+        <v>720003</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C521">
         <v>0</v>
@@ -6593,7 +6596,7 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522">
-        <v>721001</v>
+        <v>720004</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>1</v>
@@ -6604,7 +6607,7 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523">
-        <v>651030</v>
+        <v>721001</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>56</v>
@@ -6615,7 +6618,7 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524">
-        <v>651030</v>
+        <v>721001</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>30</v>
@@ -6626,54 +6629,54 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525">
-        <v>651010</v>
+        <v>721001</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C525">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526">
+        <v>651030</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C526">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A527">
+        <v>651030</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A528">
         <v>651010</v>
       </c>
-      <c r="B526" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C526">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A527" t="s">
-        <v>143</v>
-      </c>
-      <c r="B527" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C527">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A528" t="s">
-        <v>144</v>
-      </c>
       <c r="B528" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C528">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A529" t="s">
-        <v>145</v>
+      <c r="A529">
+        <v>651010</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -6681,21 +6684,21 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C530">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C531">
         <v>0</v>
@@ -6703,10 +6706,10 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C532">
         <v>0</v>
@@ -6714,10 +6717,10 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C533">
         <v>0</v>
@@ -6725,7 +6728,7 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>56</v>
@@ -6736,10 +6739,10 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C535">
         <v>0</v>
@@ -6747,10 +6750,10 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C536">
         <v>0</v>
@@ -6758,10 +6761,10 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -6769,7 +6772,7 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>30</v>
@@ -6780,21 +6783,21 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C539">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C540">
         <v>0</v>
@@ -6802,10 +6805,10 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C541">
         <v>0</v>
@@ -6813,21 +6816,21 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C542">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C543">
         <v>0</v>
@@ -6835,10 +6838,10 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C544">
         <v>0</v>
@@ -6846,35 +6849,35 @@
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C545">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C546">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C547">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -6882,26 +6885,26 @@
         <v>149</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C548">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C549">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>1</v>
@@ -6911,33 +6914,33 @@
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A551">
-        <v>721014</v>
+      <c r="A551" t="s">
+        <v>149</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C551">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A552">
-        <v>721008</v>
+      <c r="A552" t="s">
+        <v>151</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C552">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A553">
-        <v>721005</v>
+      <c r="A553" t="s">
+        <v>151</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C553">
         <v>110</v>
@@ -6945,13 +6948,13 @@
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554">
-        <v>721005</v>
+        <v>721014</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C554">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -6959,7 +6962,7 @@
         <v>721008</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C555">
         <v>60</v>
@@ -6967,29 +6970,29 @@
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556">
-        <v>721014</v>
+        <v>721005</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C556">
-        <v>50</v>
+        <v>110</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A557" t="s">
-        <v>152</v>
+      <c r="A557">
+        <v>721005</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C557">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A558" t="s">
-        <v>152</v>
+      <c r="A558">
+        <v>721008</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>1</v>
@@ -7000,79 +7003,79 @@
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559">
-        <v>241040</v>
+        <v>721014</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C559">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A560">
-        <v>241020</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>152</v>
       </c>
       <c r="B560" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C560">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A561">
-        <v>241020</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>152</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C561">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>241040</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C562">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563">
-        <v>601138</v>
+        <v>241020</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C563">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564">
-        <v>601128</v>
+        <v>241020</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C564">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565">
-        <v>601128</v>
+        <v>241040</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C565">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7080,54 +7083,54 @@
         <v>601138</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C566">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A567">
+        <v>601128</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C567">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A568">
+        <v>601128</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C568">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A569">
+        <v>601138</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C569">
         <v>60</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A567" t="s">
-        <v>153</v>
-      </c>
-      <c r="B567" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C567">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A568" t="s">
-        <v>154</v>
-      </c>
-      <c r="B568" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C568">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A569" t="s">
-        <v>155</v>
-      </c>
-      <c r="B569" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C569">
-        <v>0</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C570">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7135,20 +7138,53 @@
         <v>154</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C571">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
+        <v>155</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>155</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C573">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>154</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
         <v>153</v>
       </c>
-      <c r="B572" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C572">
+      <c r="B575" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C575">
         <v>50</v>
       </c>
     </row>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E87D85B-1814-4175-B9A0-F3CB796D2D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EA2EF0-9E7C-47E4-9F6B-95617B5B5CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29805" yWindow="615" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile_config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="178">
   <si>
     <t>GP8280</t>
   </si>
@@ -854,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C575"/>
+  <dimension ref="A1:C576"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -6860,18 +6860,18 @@
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C546">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>30</v>
@@ -6882,24 +6882,24 @@
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B548" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C548">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C549">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -6907,32 +6907,32 @@
         <v>150</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C550">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C551">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C552">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -6940,18 +6940,18 @@
         <v>151</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C553">
-        <v>110</v>
+        <v>150</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A554">
-        <v>721014</v>
+      <c r="A554" t="s">
+        <v>151</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C554">
         <v>110</v>
@@ -6959,24 +6959,24 @@
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555">
-        <v>721008</v>
+        <v>721014</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C555">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556">
-        <v>721005</v>
+        <v>721008</v>
       </c>
       <c r="B556" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C556">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -6984,15 +6984,15 @@
         <v>721005</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C557">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558">
-        <v>721008</v>
+        <v>721005</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>1</v>
@@ -7003,24 +7003,24 @@
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559">
+        <v>721008</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C559">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A560">
         <v>721014</v>
       </c>
-      <c r="B559" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C559">
+      <c r="B560" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C560">
         <v>50</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A560" t="s">
-        <v>152</v>
-      </c>
-      <c r="B560" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C560">
-        <v>110</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -7028,32 +7028,32 @@
         <v>152</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C561">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>152</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C562">
         <v>60</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A562">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A563">
         <v>241040</v>
       </c>
-      <c r="B562" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C562">
+      <c r="B563" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C563">
         <v>120</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A563">
-        <v>241020</v>
-      </c>
-      <c r="B563" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C563">
-        <v>70</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7061,43 +7061,43 @@
         <v>241020</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C564">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565">
-        <v>241040</v>
+        <v>241020</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C565">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566">
-        <v>601138</v>
+        <v>241040</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C566">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567">
-        <v>601128</v>
+        <v>601138</v>
       </c>
       <c r="B567" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C567">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7105,54 +7105,54 @@
         <v>601128</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C568">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569">
+        <v>601128</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C569">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A570">
         <v>601138</v>
       </c>
-      <c r="B569" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C569">
+      <c r="B570" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C570">
         <v>60</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A570" t="s">
-        <v>153</v>
-      </c>
-      <c r="B570" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C570">
-        <v>120</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B571" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C571">
-        <v>70</v>
+        <v>120</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B572" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C572">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7160,31 +7160,42 @@
         <v>155</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C573">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B574" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C574">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
+        <v>154</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
         <v>153</v>
       </c>
-      <c r="B575" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C575">
+      <c r="B576" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C576">
         <v>50</v>
       </c>
     </row>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EA2EF0-9E7C-47E4-9F6B-95617B5B5CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C884B0AA-0F22-46F7-A2B4-E9058805DE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29805" yWindow="615" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile_config" sheetId="1" r:id="rId1"/>
@@ -2320,7 +2320,7 @@
         <v>761016</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C133">
         <v>120</v>
@@ -2782,7 +2782,7 @@
         <v>406323</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C175">
         <v>90</v>
@@ -2969,7 +2969,7 @@
         <v>406215</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C192">
         <v>90</v>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C884B0AA-0F22-46F7-A2B4-E9058805DE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D815B97-F4EC-4074-8755-E62DC1FE79DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5081,7 +5081,7 @@
         <v>406010</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C384">
         <v>120</v>

--- a/project/config/profile_config_file.xlsx
+++ b/project/config/profile_config_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsochacki\Desktop\Python\Tkinter\production-counting\project\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D815B97-F4EC-4074-8755-E62DC1FE79DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99384611-6B88-43B4-A128-E442BFCC902C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile_config" sheetId="1" r:id="rId1"/>
@@ -855,15 +855,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C576"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="16384" max="16384" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="16384" max="16384" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -874,7 +874,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -885,7 +885,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -896,7 +896,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -907,7 +907,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -918,7 +918,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -929,7 +929,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -940,7 +940,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -951,7 +951,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -962,7 +962,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>413403</v>
       </c>
@@ -973,7 +973,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -984,7 +984,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -995,7 +995,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>413843</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>413837</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>413833</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>413829</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>413009</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>413011</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>413013</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>413015</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>413311</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>413313</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>413315</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>413411</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>413735</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>413729</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>413730</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>413111</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>413113</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>413115</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>413211</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>413209</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>413207</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>413205</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>413201</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>413001</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>413003</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>413005</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>413007</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>413309</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>413307</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>413305</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>413303</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>413301</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>443310</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>413807</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>413809</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>413813</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>413817</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>413821</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>413825</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>413728</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>413725</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>413717</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>413109</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>413107</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>413105</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>413103</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>29</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>29</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>31</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>31</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>32</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>32</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>33</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>33</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>34</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>34</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>35</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>35</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>36</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>36</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>37</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>37</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>416177</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>416177</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>416160</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>416160</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>416382</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>416382</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>426152</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>426152</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>426150</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>426150</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>426151</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>426151</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>242310</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>242310</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>416269</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>416168</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>416168</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>416157</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>416157</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>466005</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>416146</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>38</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>39</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>41</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>41</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>406225</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>406225</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>606305</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>656300</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>656305</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>42</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>726004</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>726003</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>246030</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>246030</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>726003</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>726004</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>42</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>761016</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>159</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>416269</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>160</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>161</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>162</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>163</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>164</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>165</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>166</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>167</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>168</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>169</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>170</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>170</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>169</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>167</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>166</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>165</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>164</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>163</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>161</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>160</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>43</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>44</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>45</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>46</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>46</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>45</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>44</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>43</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>47</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>47</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>416274</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>416274</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>48</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>406320</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>416330</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>406319</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>406319</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>406323</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>416251</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>416251</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>49</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>49</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>50</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>51</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>416264</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>52</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>406255</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>416026</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>53</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>54</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>55</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>55</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>57</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>57</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>406215</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>406266</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>58</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>406271</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>656330</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>59</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>406295</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>406286</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>406281</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>60</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>60</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>172</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>173</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>174</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>174</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>175</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>716317</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>706290</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>706290</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>416357</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>416337</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>416327</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>416302</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>177</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>416272</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>416272</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>666000</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>666000</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>61</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>62</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>62</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>406005</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>406005</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>716020</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>736323</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>63</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>416112</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>64</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>426100</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>64</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>426100</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>416112</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>63</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>65</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>66</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>406115</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>406115</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>666001</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>666001</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>666001</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>550801</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>553424</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>67</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>68</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>68</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>176</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>69</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>70</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>71</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>72</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>721015</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>721009</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>341040</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>341030</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>341030</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>341040</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>721009</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>721015</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>72</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>71</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>70</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>69</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>73</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>74</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>74</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>73</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>75</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>76</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>77</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>720024</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>720022</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>78</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>79</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>661000</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>661000</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>78</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>79</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>720022</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>720024</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>77</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>76</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>75</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>80</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>416210</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>416210</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>80</v>
       </c>
@@ -4020,18 +4020,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>406210</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C288">
         <v>100</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>650050</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>650040</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>650040</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>650040</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>650050</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>650050</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>650020</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>650020</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>600138</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>600138</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>600121</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>600127</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>600227</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>600227</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>600127</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>600121</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>600128</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>600128</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>650030</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>650030</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>660000</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>660000</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>82</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>82</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>83</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>83</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>83</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>82</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>406670</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>406670</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>406316</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>84</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>84</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>85</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>85</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>86</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>550800</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>87</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>88</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>89</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>90</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>91</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>92</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>93</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>720023</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>94</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>240040</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>240030</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>240020</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>240020</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>240030</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>240040</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>94</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>720023</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>93</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>92</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>91</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>90</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>89</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>88</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>87</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>95</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>96</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>97</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>97</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>96</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>95</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>722010</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>722005</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>722006</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>722000</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>722000</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>722006</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>722005</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>722010</v>
       </c>
@@ -4856,7 +4856,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>98</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>99</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>100</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>101</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>101</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>100</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>99</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>98</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>102</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>103</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>104</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>105</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>105</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>104</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>103</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>102</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>106</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>107</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>107</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>106</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>406010</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>406321</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>406660</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>406329</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>406325</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>416240</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>416240</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>108</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>109</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>109</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>110</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>110</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>111</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>111</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>112</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>112</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>113</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>113</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>242320</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>242320</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>651050</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>651050</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>730010</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>730010</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>731020</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>731020</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>476273</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>476273</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>114</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>114</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>466009</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>466009</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>416273</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>416273</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>466023</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>466023</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>426200</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>426200</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>406272</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>406272</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>115</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>115</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>116</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>116</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>117</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>117</v>
       </c>
@@ -5582,7 +5582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>416338</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>416331</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>416065</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>416067</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>416086</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>416096</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>118</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>666003</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>666002</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>119</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>416070</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>416069</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>120</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>406340</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>416301</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>416119</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>406081</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>416068</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>416068</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>736315</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>736334</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>121</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>406307</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>466400</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>416139</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>416139</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>416148</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>122</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>123</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>124</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>125</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>126</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>127</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>128</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>171</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>406310</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>129</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>416180</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>606180</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>656310</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>416311</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>406157</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>416182</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>406315</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>406312</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>130</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>131</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>131</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>130</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>762013</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>762013</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>132</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>132</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>133</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>133</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>134</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>134</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>242020</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>242020</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>602010</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>602010</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>652010</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>652010</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>135</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>136</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>137</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>138</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>135</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>136</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>137</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>138</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>138</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>137</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>136</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>135</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>139</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>140</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>141</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>139</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>140</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>141</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>141</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>140</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>139</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>142</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>142</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>142</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>720004</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>720003</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>720004</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>720003</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>720003</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>720004</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>721001</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>721001</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>721001</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>651030</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>651030</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>651010</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>651010</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>143</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>144</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>145</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>146</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>143</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>144</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>145</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>146</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>143</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>144</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>145</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>146</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>147</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>148</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>147</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>148</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>149</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>147</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>148</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>149</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>150</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>150</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>149</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>151</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>151</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>721014</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>721008</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>721005</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>721005</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>721008</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>721014</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>152</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>152</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>241040</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>241020</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>241020</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566">
         <v>241040</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>601138</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>601128</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>601128</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>601138</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>153</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>154</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>155</v>
       </c>
@@ -7166,7 +7166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>155</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>154</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>153</v>
       </c>
